--- a/02_Dataset_EDA_Feature_UMAP_Mahalanobis/"distance" from new FeCrNiMoTi data
to hardness dataset.xlsx
+++ b/02_Dataset_EDA_Feature_UMAP_Mahalanobis/"distance" from new FeCrNiMoTi data
to hardness dataset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,181 +425,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF70"/>
+  <dimension ref="A1:AE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>V</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ta</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Ta</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>Hf</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Hf</t>
+          <t>delta_a</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>delta_a</t>
+          <t>Tm</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Tm</t>
+          <t>sigma_Tm</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sigma_Tm</t>
+          <t>Hmix</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Hmix</t>
+          <t>sigma_Hmix</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>sigma_Hmix</t>
+          <t>sigma_elec_nega</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>sigma_elec_nega</t>
+          <t>VEC</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>VEC</t>
+          <t>sigma_VEC</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sigma_VEC</t>
+          <t>Mahalanobis</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Mahalanobis</t>
+          <t>p value</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>p value</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>UMAP Component 1</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>UMAP Component 1</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>UMAP Component 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>680</v>
+      <c r="A2" t="n">
+        <v>14.31699359657089</v>
       </c>
       <c r="B2" t="n">
-        <v>14.31699359657089</v>
+        <v>35.21024747388501</v>
       </c>
       <c r="C2" t="n">
-        <v>35.21024747388501</v>
+        <v>45.45303756381198</v>
       </c>
       <c r="D2" t="n">
-        <v>45.45303756381198</v>
+        <v>4.138939456436662</v>
       </c>
       <c r="E2" t="n">
-        <v>4.138939456436662</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.8807819092954645</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8807819092954645</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -641,65 +641,62 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.02253547848829161</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02253547848829161</v>
+        <v>1943.689937272888</v>
       </c>
       <c r="U2" t="n">
-        <v>1943.689937272888</v>
+        <v>257.6622314272465</v>
       </c>
       <c r="V2" t="n">
-        <v>257.6622314272465</v>
+        <v>-6.600670779576464</v>
       </c>
       <c r="W2" t="n">
-        <v>-6.600670779576464</v>
+        <v>2.725194759728065</v>
       </c>
       <c r="X2" t="n">
-        <v>2.725194759728065</v>
+        <v>0.1294765609887398</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1294765609887398</v>
+        <v>8.019565087964157</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.019565087964157</v>
+        <v>1.882782738202394</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.882782738202394</v>
+        <v>27.16288804318787</v>
       </c>
       <c r="AB2" t="n">
-        <v>27.16288804759034</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.263728570566336e-06</v>
-      </c>
-      <c r="AD2" t="inlineStr">
+        <v>1.263728573341893e-06</v>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD2" t="n">
+        <v>0.7868250608444214</v>
+      </c>
       <c r="AE2" t="n">
-        <v>2.17266321182251</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>6.01155424118042</v>
+        <v>8.364902496337891</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>681</v>
+      <c r="A3" t="n">
+        <v>15.27891067420843</v>
       </c>
       <c r="B3" t="n">
-        <v>15.27891067420843</v>
+        <v>36.6201454088738</v>
       </c>
       <c r="C3" t="n">
-        <v>36.6201454088738</v>
+        <v>40.92255698837002</v>
       </c>
       <c r="D3" t="n">
-        <v>40.92255698837002</v>
+        <v>5.876322025641183</v>
       </c>
       <c r="E3" t="n">
-        <v>5.876322025641183</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -726,10 +723,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.302064902906558</v>
       </c>
       <c r="O3" t="n">
-        <v>1.302064902906558</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -741,65 +738,62 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.02694522627737901</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02694522627737901</v>
+        <v>1965.232211811153</v>
       </c>
       <c r="U3" t="n">
-        <v>1965.232211811153</v>
+        <v>272.8648425860655</v>
       </c>
       <c r="V3" t="n">
-        <v>272.8648425860655</v>
+        <v>-6.784358711655282</v>
       </c>
       <c r="W3" t="n">
-        <v>-6.784358711655282</v>
+        <v>3.05867883644598</v>
       </c>
       <c r="X3" t="n">
-        <v>3.05867883644598</v>
+        <v>0.1352538527876291</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1352538527876291</v>
+        <v>7.860844830357834</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.860844830357834</v>
+        <v>1.882863745105841</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.882863745105841</v>
+        <v>25.12998731785099</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.12998732675665</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.492147563233239e-06</v>
-      </c>
-      <c r="AD3" t="inlineStr">
+        <v>3.492147578776361e-06</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD3" t="n">
+        <v>0.8145485520362854</v>
+      </c>
       <c r="AE3" t="n">
-        <v>2.262024402618408</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>6.16260814666748</v>
+        <v>8.568320274353027</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>682</v>
+      <c r="A4" t="n">
+        <v>15.85974020072816</v>
       </c>
       <c r="B4" t="n">
-        <v>15.85974020072816</v>
+        <v>36.64321598420395</v>
       </c>
       <c r="C4" t="n">
-        <v>36.64321598420395</v>
+        <v>37.76174814854082</v>
       </c>
       <c r="D4" t="n">
-        <v>37.76174814854082</v>
+        <v>7.80394955983821</v>
       </c>
       <c r="E4" t="n">
-        <v>7.80394955983821</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -826,10 +820,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.931346106688842</v>
       </c>
       <c r="O4" t="n">
-        <v>1.931346106688842</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -841,65 +835,62 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.03182150005173198</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03182150005173198</v>
+        <v>1982.136990951654</v>
       </c>
       <c r="U4" t="n">
-        <v>1982.136990951654</v>
+        <v>287.9882959816393</v>
       </c>
       <c r="V4" t="n">
-        <v>287.9882959816393</v>
+        <v>-7.110372733273778</v>
       </c>
       <c r="W4" t="n">
-        <v>-7.110372733273778</v>
+        <v>3.472869202386087</v>
       </c>
       <c r="X4" t="n">
-        <v>3.472869202386087</v>
+        <v>0.1415133348130074</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1415133348130074</v>
+        <v>7.745255241435793</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.745255241435793</v>
+        <v>1.88771008374703</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88771008374703</v>
+        <v>22.50042302881769</v>
       </c>
       <c r="AB4" t="n">
-        <v>22.50042303915198</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.300454664698858e-05</v>
-      </c>
-      <c r="AD4" t="inlineStr">
+        <v>1.300454671415707e-05</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD4" t="n">
+        <v>0.7828209400177002</v>
+      </c>
       <c r="AE4" t="n">
-        <v>2.401015520095825</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>6.092511177062988</v>
+        <v>8.785611152648926</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>683</v>
+      <c r="A5" t="n">
+        <v>16.6254486072678</v>
       </c>
       <c r="B5" t="n">
-        <v>16.6254486072678</v>
+        <v>36.11907612318919</v>
       </c>
       <c r="C5" t="n">
-        <v>36.11907612318919</v>
+        <v>34.64032304241116</v>
       </c>
       <c r="D5" t="n">
-        <v>34.64032304241116</v>
+        <v>9.938243812179149</v>
       </c>
       <c r="E5" t="n">
-        <v>9.938243812179149</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -926,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.676908414952717</v>
       </c>
       <c r="O5" t="n">
-        <v>2.676908414952717</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -941,65 +932,62 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.03650958141869901</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03650958141869901</v>
+        <v>1998.704549708214</v>
       </c>
       <c r="U5" t="n">
-        <v>1998.704549708214</v>
+        <v>303.2036733109156</v>
       </c>
       <c r="V5" t="n">
-        <v>303.2036733109156</v>
+        <v>-7.448384251476015</v>
       </c>
       <c r="W5" t="n">
-        <v>-7.448384251476015</v>
+        <v>3.870669819197705</v>
       </c>
       <c r="X5" t="n">
-        <v>3.870669819197705</v>
+        <v>0.1481363288949336</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1481363288949336</v>
+        <v>7.632754295458397</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.632754295458397</v>
+        <v>1.888592288927109</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.888592288927109</v>
+        <v>20.2582233609476</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.25822337752354</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.990089956784626e-05</v>
-      </c>
-      <c r="AD5" t="inlineStr">
+        <v>3.99008998985817e-05</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD5" t="n">
+        <v>0.7034962177276611</v>
+      </c>
       <c r="AE5" t="n">
-        <v>2.52386474609375</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6.271859169006348</v>
+        <v>8.911354064941406</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>684</v>
+      <c r="A6" t="n">
+        <v>16.72168606967666</v>
       </c>
       <c r="B6" t="n">
-        <v>16.72168606967666</v>
+        <v>34.35963304036784</v>
       </c>
       <c r="C6" t="n">
-        <v>34.35963304036784</v>
+        <v>32.01806283446086</v>
       </c>
       <c r="D6" t="n">
-        <v>32.01806283446086</v>
+        <v>13.07589480250266</v>
       </c>
       <c r="E6" t="n">
-        <v>13.07589480250266</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1026,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.824723252991968</v>
       </c>
       <c r="O6" t="n">
-        <v>3.824723252991968</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1041,65 +1029,62 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.04235576111430078</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04235576111430078</v>
+        <v>2018.214448345743</v>
       </c>
       <c r="U6" t="n">
-        <v>2018.214448345743</v>
+        <v>324.7308784847411</v>
       </c>
       <c r="V6" t="n">
-        <v>324.7308784847411</v>
+        <v>-8.088070431069365</v>
       </c>
       <c r="W6" t="n">
-        <v>-8.088070431069365</v>
+        <v>4.40855312851456</v>
       </c>
       <c r="X6" t="n">
-        <v>4.40855312851456</v>
+        <v>0.1577895466199948</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1577895466199948</v>
+        <v>7.522190808934131</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.522190808934131</v>
+        <v>1.906034934854781</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.906034934854781</v>
+        <v>18.08894479837711</v>
       </c>
       <c r="AB6" t="n">
-        <v>18.0889448159358</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0001180417233873632</v>
-      </c>
-      <c r="AD6" t="inlineStr">
+        <v>0.0001180417244236454</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD6" t="n">
+        <v>0.7095375657081604</v>
+      </c>
       <c r="AE6" t="n">
-        <v>2.728684663772583</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6.449848175048828</v>
+        <v>9.175928115844727</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>685</v>
+      <c r="A7" t="n">
+        <v>17.58023045110392</v>
       </c>
       <c r="B7" t="n">
-        <v>17.58023045110392</v>
+        <v>25.78737383125358</v>
       </c>
       <c r="C7" t="n">
-        <v>25.78737383125358</v>
+        <v>52.95340249452182</v>
       </c>
       <c r="D7" t="n">
-        <v>52.95340249452182</v>
+        <v>3.020229760012374</v>
       </c>
       <c r="E7" t="n">
-        <v>3.020229760012374</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1126,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.6587634631082945</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6587634631082945</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1141,65 +1126,62 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.01965435998709447</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01965435998709447</v>
+        <v>1892.938009525173</v>
       </c>
       <c r="U7" t="n">
-        <v>1892.938009525173</v>
+        <v>237.5653691001578</v>
       </c>
       <c r="V7" t="n">
-        <v>237.5653691001578</v>
+        <v>-5.994507720450255</v>
       </c>
       <c r="W7" t="n">
-        <v>-5.994507720450255</v>
+        <v>2.581847742723802</v>
       </c>
       <c r="X7" t="n">
-        <v>2.581847742723802</v>
+        <v>0.118462799182464</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.118462799182464</v>
+        <v>8.395015690413882</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.395015690413882</v>
+        <v>1.794908847638016</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.794908847638016</v>
+        <v>20.98415453040579</v>
       </c>
       <c r="AB7" t="n">
-        <v>20.9841545353461</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.775547978117743e-05</v>
-      </c>
-      <c r="AD7" t="inlineStr">
+        <v>2.775547984978921e-05</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD7" t="n">
+        <v>0.5242705345153809</v>
+      </c>
       <c r="AE7" t="n">
-        <v>2.149840831756592</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>5.65466833114624</v>
+        <v>8.203737258911133</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>686</v>
+      <c r="A8" t="n">
+        <v>18.57818076528054</v>
       </c>
       <c r="B8" t="n">
-        <v>18.57818076528054</v>
+        <v>27.91436124376087</v>
       </c>
       <c r="C8" t="n">
-        <v>27.91436124376087</v>
+        <v>48.96939004892192</v>
       </c>
       <c r="D8" t="n">
-        <v>48.96939004892192</v>
+        <v>3.715176746073181</v>
       </c>
       <c r="E8" t="n">
-        <v>3.715176746073181</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1226,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.8228911959634791</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8228911959634791</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1241,65 +1223,62 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.0217918802475133</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0217918802475133</v>
+        <v>1909.362930638625</v>
       </c>
       <c r="U8" t="n">
-        <v>1909.362930638625</v>
+        <v>247.3803952796019</v>
       </c>
       <c r="V8" t="n">
-        <v>247.3803952796019</v>
+        <v>-6.183842717090982</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.183842717090982</v>
+        <v>2.759795499553948</v>
       </c>
       <c r="X8" t="n">
-        <v>2.759795499553948</v>
+        <v>0.1223855138317489</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1223855138317489</v>
+        <v>8.255002054743926</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.255002054743926</v>
+        <v>1.81549624662442</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81549624662442</v>
+        <v>18.95484261328538</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.95484262431203</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.656111002574129e-05</v>
-      </c>
-      <c r="AD8" t="inlineStr">
+        <v>7.656111044784808e-05</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD8" t="n">
+        <v>0.5040947794914246</v>
+      </c>
       <c r="AE8" t="n">
-        <v>2.400177478790283</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>5.719884395599365</v>
+        <v>8.371829986572266</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>687</v>
+      <c r="A9" t="n">
+        <v>19.60838259075554</v>
       </c>
       <c r="B9" t="n">
-        <v>19.60838259075554</v>
+        <v>29.66754518388709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.66754518388709</v>
+        <v>43.89614162525374</v>
       </c>
       <c r="D9" t="n">
-        <v>43.89614162525374</v>
+        <v>5.44038604100223</v>
       </c>
       <c r="E9" t="n">
-        <v>5.44038604100223</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1326,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.38754455910141</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38754455910141</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1341,65 +1320,62 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.0272568340717355</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0272568340717355</v>
+        <v>1932.778266653697</v>
       </c>
       <c r="U9" t="n">
-        <v>1932.778266653697</v>
+        <v>265.8434854610491</v>
       </c>
       <c r="V9" t="n">
-        <v>265.8434854610491</v>
+        <v>-6.625733508060049</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.625733508060049</v>
+        <v>3.244590676251661</v>
       </c>
       <c r="X9" t="n">
-        <v>3.244590676251661</v>
+        <v>0.1295903888532182</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1295903888532182</v>
+        <v>8.071379240315668</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.071379240315668</v>
+        <v>1.841990243468286</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.841990243468286</v>
+        <v>16.06064106577704</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.06064107639279</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.0003254438750071031</v>
-      </c>
-      <c r="AD9" t="inlineStr">
+        <v>0.0003254438767344991</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD9" t="n">
+        <v>0.4150807857513428</v>
+      </c>
       <c r="AE9" t="n">
-        <v>2.606870174407959</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>5.96914529800415</v>
+        <v>8.596756935119629</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>688</v>
+      <c r="A10" t="n">
+        <v>20.10500298210745</v>
       </c>
       <c r="B10" t="n">
-        <v>20.10500298210745</v>
+        <v>29.98729806356584</v>
       </c>
       <c r="C10" t="n">
-        <v>29.98729806356584</v>
+        <v>40.7223095709536</v>
       </c>
       <c r="D10" t="n">
-        <v>40.7223095709536</v>
+        <v>7.226526681518458</v>
       </c>
       <c r="E10" t="n">
-        <v>7.226526681518458</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1426,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.958862701854644</v>
       </c>
       <c r="O10" t="n">
-        <v>1.958862701854644</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1441,65 +1417,62 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.0317465603588726</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0317465603588726</v>
+        <v>1949.68899993882</v>
       </c>
       <c r="U10" t="n">
-        <v>1949.68899993882</v>
+        <v>282.152996096776</v>
       </c>
       <c r="V10" t="n">
-        <v>282.152996096776</v>
+        <v>-7.013371196182621</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.013371196182621</v>
+        <v>3.636039064216791</v>
       </c>
       <c r="X10" t="n">
-        <v>3.636039064216791</v>
+        <v>0.1358791131797596</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1358791131797596</v>
+        <v>7.954126347312227</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.954126347312227</v>
+        <v>1.858662341015401</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.858662341015401</v>
+        <v>14.19234061867621</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.19234062996603</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.0008282708736548905</v>
-      </c>
-      <c r="AD10" t="inlineStr">
+        <v>0.0008282708783304837</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD10" t="n">
+        <v>0.4738653302192688</v>
+      </c>
       <c r="AE10" t="n">
-        <v>2.656509876251221</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>6.03134822845459</v>
+        <v>8.794034957885742</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>689</v>
+      <c r="A11" t="n">
+        <v>20.82282672295324</v>
       </c>
       <c r="B11" t="n">
-        <v>20.82282672295324</v>
+        <v>29.84803147986053</v>
       </c>
       <c r="C11" t="n">
-        <v>29.84803147986053</v>
+        <v>36.74628169506838</v>
       </c>
       <c r="D11" t="n">
-        <v>36.74628169506838</v>
+        <v>9.683662142563847</v>
       </c>
       <c r="E11" t="n">
-        <v>9.683662142563847</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1526,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.899197959554011</v>
       </c>
       <c r="O11" t="n">
-        <v>2.899197959554011</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1541,65 +1514,62 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.03747469633312293</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03747469633312293</v>
+        <v>1970.837222367484</v>
       </c>
       <c r="U11" t="n">
-        <v>1970.837222367484</v>
+        <v>301.8142356671538</v>
       </c>
       <c r="V11" t="n">
-        <v>301.8142356671538</v>
+        <v>-7.569709028266014</v>
       </c>
       <c r="W11" t="n">
-        <v>-7.569709028266014</v>
+        <v>4.14684298561076</v>
       </c>
       <c r="X11" t="n">
-        <v>4.14684298561076</v>
+        <v>0.144266728071026</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.144266728071026</v>
+        <v>7.803943277815693</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.803943277815693</v>
+        <v>1.876353876773989</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.876353876773989</v>
+        <v>12.6507362794223</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.65073628840253</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.001790307038051497</v>
-      </c>
-      <c r="AD11" t="inlineStr">
+        <v>0.001790307046090178</v>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD11" t="n">
+        <v>0.4250524640083313</v>
+      </c>
       <c r="AE11" t="n">
-        <v>2.819504976272583</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>6.277555465698242</v>
+        <v>9.078433990478516</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>690</v>
+      <c r="A12" t="n">
+        <v>21.05931589769223</v>
       </c>
       <c r="B12" t="n">
-        <v>21.05931589769223</v>
+        <v>29.32188193594872</v>
       </c>
       <c r="C12" t="n">
-        <v>29.32188193594872</v>
+        <v>33.80936172608322</v>
       </c>
       <c r="D12" t="n">
-        <v>33.80936172608322</v>
+        <v>11.33506169200627</v>
       </c>
       <c r="E12" t="n">
-        <v>11.33506169200627</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1626,10 +1596,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.474378748269556</v>
       </c>
       <c r="O12" t="n">
-        <v>4.474378748269556</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1641,65 +1611,62 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.04388062762971051</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04388062762971051</v>
+        <v>1984.893645274819</v>
       </c>
       <c r="U12" t="n">
-        <v>1984.893645274819</v>
+        <v>312.7912526964028</v>
       </c>
       <c r="V12" t="n">
-        <v>312.7912526964028</v>
+        <v>-8.544522616153612</v>
       </c>
       <c r="W12" t="n">
-        <v>-8.544522616153612</v>
+        <v>4.828722472818985</v>
       </c>
       <c r="X12" t="n">
-        <v>4.828722472818985</v>
+        <v>0.1518851483776252</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1518851483776252</v>
+        <v>7.661042526388837</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.661042526388837</v>
+        <v>1.913479908641325</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.913479908641325</v>
+        <v>12.25373486932471</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.25373488065375</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.002183409920936352</v>
-      </c>
-      <c r="AD12" t="inlineStr">
+        <v>0.002183409933304237</v>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD12" t="n">
+        <v>0.501504123210907</v>
+      </c>
       <c r="AE12" t="n">
-        <v>2.905865430831909</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6.632551193237305</v>
+        <v>9.401344299316406</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>691</v>
+      <c r="A13" t="n">
+        <v>21.38449445236935</v>
       </c>
       <c r="B13" t="n">
-        <v>21.38449445236935</v>
+        <v>26.75493744727493</v>
       </c>
       <c r="C13" t="n">
-        <v>26.75493744727493</v>
+        <v>30.80309232937815</v>
       </c>
       <c r="D13" t="n">
-        <v>30.80309232937815</v>
+        <v>14.61315841043162</v>
       </c>
       <c r="E13" t="n">
-        <v>14.61315841043162</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1726,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.444317360545956</v>
       </c>
       <c r="O13" t="n">
-        <v>6.444317360545956</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1741,65 +1708,62 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.05066928667504613</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05066928667504613</v>
+        <v>2003.518849764438</v>
       </c>
       <c r="U13" t="n">
-        <v>2003.518849764438</v>
+        <v>335.0663881607878</v>
       </c>
       <c r="V13" t="n">
-        <v>335.0663881607878</v>
+        <v>-9.696165162328283</v>
       </c>
       <c r="W13" t="n">
-        <v>-9.696165162328283</v>
+        <v>5.529627551909936</v>
       </c>
       <c r="X13" t="n">
-        <v>5.529627551909936</v>
+        <v>0.1630674105518073</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1630674105518073</v>
+        <v>7.518731247211837</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.518731247211837</v>
+        <v>1.953826742856776</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.953826742856776</v>
+        <v>12.32037620038973</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.32037621843238</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.00211185597479413</v>
-      </c>
-      <c r="AD13" t="inlineStr">
+        <v>0.00211185599384589</v>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD13" t="n">
+        <v>0.4005688726902008</v>
+      </c>
       <c r="AE13" t="n">
-        <v>3.119555234909058</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>6.843473434448242</v>
+        <v>9.751543998718262</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>692</v>
+      <c r="A14" t="n">
+        <v>19.79697020692051</v>
       </c>
       <c r="B14" t="n">
-        <v>19.79697020692051</v>
+        <v>17.07053042259378</v>
       </c>
       <c r="C14" t="n">
-        <v>17.07053042259378</v>
+        <v>60.47274407694169</v>
       </c>
       <c r="D14" t="n">
-        <v>60.47274407694169</v>
+        <v>2.127756037006</v>
       </c>
       <c r="E14" t="n">
-        <v>2.127756037006</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1826,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.5319992565380067</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5319992565380067</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1841,65 +1805,62 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.01739704546744002</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01739704546744002</v>
+        <v>1846.004872720977</v>
       </c>
       <c r="U14" t="n">
-        <v>1846.004872720977</v>
+        <v>208.545571495524</v>
       </c>
       <c r="V14" t="n">
-        <v>208.545571495524</v>
+        <v>-5.094679961225656</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.094679961225656</v>
+        <v>2.418353126284907</v>
       </c>
       <c r="X14" t="n">
-        <v>2.418353126284907</v>
+        <v>0.1040068291739516</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1040068291739516</v>
+        <v>8.753101635493774</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.753101635493774</v>
+        <v>1.642333751820618</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.642333751820618</v>
+        <v>25.08374099325601</v>
       </c>
       <c r="AB14" t="n">
-        <v>25.08374099660083</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.573837897508092e-06</v>
-      </c>
-      <c r="AD14" t="inlineStr">
+        <v>3.573837903503296e-06</v>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD14" t="n">
+        <v>0.02673215046525002</v>
+      </c>
       <c r="AE14" t="n">
-        <v>2.133790493011475</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>5.134836196899414</v>
+        <v>7.741844654083252</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>693</v>
+      <c r="A15" t="n">
+        <v>21.48203443327129</v>
       </c>
       <c r="B15" t="n">
-        <v>21.48203443327129</v>
+        <v>19.81963700745474</v>
       </c>
       <c r="C15" t="n">
-        <v>19.81963700745474</v>
+        <v>55.11019986941908</v>
       </c>
       <c r="D15" t="n">
-        <v>55.11019986941908</v>
+        <v>2.952438189314062</v>
       </c>
       <c r="E15" t="n">
-        <v>2.952438189314062</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1926,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.6356905005408267</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6356905005408267</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1941,65 +1902,62 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.01947690848130699</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01947690848130699</v>
+        <v>1866.941193872086</v>
       </c>
       <c r="U15" t="n">
-        <v>1866.941193872086</v>
+        <v>226.026125736655</v>
       </c>
       <c r="V15" t="n">
-        <v>226.026125736655</v>
+        <v>-5.44141286813749</v>
       </c>
       <c r="W15" t="n">
-        <v>-5.44141286813749</v>
+        <v>2.569150380285394</v>
       </c>
       <c r="X15" t="n">
-        <v>2.569150380285394</v>
+        <v>0.1104513402409985</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1104513402409985</v>
+        <v>8.572316199529583</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.572316199529583</v>
+        <v>1.698161567663727</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.698161567663727</v>
+        <v>18.53102330402433</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.53102330796985</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.463230459594296e-05</v>
-      </c>
-      <c r="AD15" t="inlineStr">
+        <v>9.463230478257145e-05</v>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD15" t="n">
+        <v>0.003679963760077953</v>
+      </c>
       <c r="AE15" t="n">
-        <v>2.301736354827881</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>5.242356777191162</v>
+        <v>8.065220832824707</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>694</v>
+      <c r="A16" t="n">
+        <v>22.47631622738632</v>
       </c>
       <c r="B16" t="n">
-        <v>22.47631622738632</v>
+        <v>21.10763041551644</v>
       </c>
       <c r="C16" t="n">
-        <v>21.10763041551644</v>
+        <v>49.48554879162086</v>
       </c>
       <c r="D16" t="n">
-        <v>49.48554879162086</v>
+        <v>5.80868725953725</v>
       </c>
       <c r="E16" t="n">
-        <v>5.80868725953725</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2026,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.121817305939112</v>
       </c>
       <c r="O16" t="n">
-        <v>1.121817305939112</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2041,65 +1999,62 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.02614807216016998</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02614807216016998</v>
+        <v>1896.591610650031</v>
       </c>
       <c r="U16" t="n">
-        <v>1896.591610650031</v>
+        <v>262.9862156880844</v>
       </c>
       <c r="V16" t="n">
-        <v>262.9862156880844</v>
+        <v>-6.066504624882788</v>
       </c>
       <c r="W16" t="n">
-        <v>-6.066504624882788</v>
+        <v>3.110339246432172</v>
       </c>
       <c r="X16" t="n">
-        <v>3.110339246432172</v>
+        <v>0.1214845237525694</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1214845237525694</v>
+        <v>8.380020178311289</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.380020178311289</v>
+        <v>1.757842370440394</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.757842370440394</v>
+        <v>13.289601331253</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.28960134234261</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.001300767672919312</v>
-      </c>
-      <c r="AD16" t="inlineStr">
+        <v>0.001300767680131876</v>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD16" t="n">
+        <v>-0.005469319876283407</v>
+      </c>
       <c r="AE16" t="n">
-        <v>2.779004573822021</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>5.40443754196167</v>
+        <v>8.460897445678711</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>695</v>
+      <c r="A17" t="n">
+        <v>24.35763244318183</v>
       </c>
       <c r="B17" t="n">
-        <v>24.35763244318183</v>
+        <v>23.1342762500515</v>
       </c>
       <c r="C17" t="n">
-        <v>23.1342762500515</v>
+        <v>46.36788004968805</v>
       </c>
       <c r="D17" t="n">
-        <v>46.36788004968805</v>
+        <v>4.638314862611241</v>
       </c>
       <c r="E17" t="n">
-        <v>4.638314862611241</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2126,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.50189639446737</v>
       </c>
       <c r="O17" t="n">
-        <v>1.50189639446737</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2141,65 +2096,62 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.02740953437875311</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02740953437875311</v>
+        <v>1899.607557974005</v>
       </c>
       <c r="U17" t="n">
-        <v>1899.607557974005</v>
+        <v>250.33118776717</v>
       </c>
       <c r="V17" t="n">
-        <v>250.33118776717</v>
+        <v>-6.338153193151018</v>
       </c>
       <c r="W17" t="n">
-        <v>-6.338153193151018</v>
+        <v>3.397307173723182</v>
       </c>
       <c r="X17" t="n">
-        <v>3.397307173723182</v>
+        <v>0.1213911037671031</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1213911037671031</v>
+        <v>8.2672917255691</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.2672917255691</v>
+        <v>1.774013157089227</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.774013157089227</v>
+        <v>11.48735232634181</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.48735233996527</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.003202971936629995</v>
-      </c>
-      <c r="AD17" t="inlineStr">
+        <v>0.003202971958447765</v>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD17" t="n">
+        <v>0.1341671794652939</v>
+      </c>
       <c r="AE17" t="n">
-        <v>2.645986795425415</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>5.687008380889893</v>
+        <v>8.648018836975098</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>696</v>
+      <c r="A18" t="n">
+        <v>25.62064236797445</v>
       </c>
       <c r="B18" t="n">
-        <v>25.62064236797445</v>
+        <v>24.03624459585487</v>
       </c>
       <c r="C18" t="n">
-        <v>24.03624459585487</v>
+        <v>41.97813069728873</v>
       </c>
       <c r="D18" t="n">
-        <v>41.97813069728873</v>
+        <v>6.326179121394539</v>
       </c>
       <c r="E18" t="n">
-        <v>6.326179121394539</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2226,10 +2178,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.038803217487418</v>
       </c>
       <c r="O18" t="n">
-        <v>2.038803217487418</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2241,65 +2193,62 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.03167846258577671</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03167846258577671</v>
+        <v>1918.914538936323</v>
       </c>
       <c r="U18" t="n">
-        <v>1918.914538936323</v>
+        <v>268.6088083257904</v>
       </c>
       <c r="V18" t="n">
-        <v>268.6088083257904</v>
+        <v>-6.728312662984566</v>
       </c>
       <c r="W18" t="n">
-        <v>-6.728312662984566</v>
+        <v>3.750063930849105</v>
       </c>
       <c r="X18" t="n">
-        <v>3.750063930849105</v>
+        <v>0.1280679896451321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1280679896451321</v>
+        <v>8.116719928551362</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.116719928551362</v>
+        <v>1.796536213617284</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.796536213617284</v>
+        <v>9.451195497614702</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.451195502742435</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.00886541301299193</v>
-      </c>
-      <c r="AD18" t="inlineStr">
+        <v>0.008865413035721748</v>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD18" t="n">
+        <v>0.1725191473960876</v>
+      </c>
       <c r="AE18" t="n">
-        <v>2.881319522857666</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>5.892768859863281</v>
+        <v>8.910874366760254</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>697</v>
+      <c r="A19" t="n">
+        <v>25.92967709475499</v>
       </c>
       <c r="B19" t="n">
-        <v>25.92967709475499</v>
+        <v>24.05215305523166</v>
       </c>
       <c r="C19" t="n">
-        <v>24.05215305523166</v>
+        <v>38.37767536798972</v>
       </c>
       <c r="D19" t="n">
-        <v>38.37767536798972</v>
+        <v>8.241916587025901</v>
       </c>
       <c r="E19" t="n">
-        <v>8.241916587025901</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2326,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.39857789499773</v>
       </c>
       <c r="O19" t="n">
-        <v>3.39857789499773</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2341,65 +2290,62 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.03883073678720245</v>
       </c>
       <c r="T19" t="n">
-        <v>0.03883073678720245</v>
+        <v>1936.944520901957</v>
       </c>
       <c r="U19" t="n">
-        <v>1936.944520901957</v>
+        <v>286.114727429456</v>
       </c>
       <c r="V19" t="n">
-        <v>286.114727429456</v>
+        <v>-7.752075638070175</v>
       </c>
       <c r="W19" t="n">
-        <v>-7.752075638070175</v>
+        <v>4.499828510959734</v>
       </c>
       <c r="X19" t="n">
-        <v>4.499828510959734</v>
+        <v>0.1371385668757474</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1371385668757474</v>
+        <v>7.957869280171375</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.957869280171375</v>
+        <v>1.849247090506852</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.849247090506852</v>
+        <v>8.479326530009057</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.479326541128106</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.01441244412029352</v>
-      </c>
-      <c r="AD19" t="inlineStr">
+        <v>0.01441244420041976</v>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD19" t="n">
+        <v>0.2140440195798874</v>
+      </c>
       <c r="AE19" t="n">
-        <v>3.062301635742188</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6.280838489532471</v>
+        <v>9.281720161437988</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>698</v>
+      <c r="A20" t="n">
+        <v>26.19588155013293</v>
       </c>
       <c r="B20" t="n">
-        <v>26.19588155013293</v>
+        <v>23.85042246394621</v>
       </c>
       <c r="C20" t="n">
-        <v>23.85042246394621</v>
+        <v>34.94838751010904</v>
       </c>
       <c r="D20" t="n">
-        <v>34.94838751010904</v>
+        <v>10.21302186693367</v>
       </c>
       <c r="E20" t="n">
-        <v>10.21302186693367</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2426,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.79228660887816</v>
       </c>
       <c r="O20" t="n">
-        <v>4.79228660887816</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2441,65 +2387,62 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.04461186343544311</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04461186343544311</v>
+        <v>1954.568006482204</v>
       </c>
       <c r="U20" t="n">
-        <v>1954.568006482204</v>
+        <v>302.1329935124126</v>
       </c>
       <c r="V20" t="n">
-        <v>302.1329935124126</v>
+        <v>-8.660219988523375</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.660219988523375</v>
+        <v>5.066392016039306</v>
       </c>
       <c r="X20" t="n">
-        <v>5.066392016039306</v>
+        <v>0.1457353177332849</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1457353177332849</v>
+        <v>7.803526696195461</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.803526696195461</v>
+        <v>1.889766506706896</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.889766506706896</v>
+        <v>8.530488817924141</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.530488831161325</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.01404843305746917</v>
-      </c>
-      <c r="AD20" t="inlineStr">
+        <v>0.01404843315045001</v>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD20" t="n">
+        <v>0.3075076341629028</v>
+      </c>
       <c r="AE20" t="n">
-        <v>3.230054616928101</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>6.692066192626953</v>
+        <v>9.65455150604248</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>699</v>
+      <c r="A21" t="n">
+        <v>25.87267490890685</v>
       </c>
       <c r="B21" t="n">
-        <v>25.87267490890685</v>
+        <v>22.74622041857604</v>
       </c>
       <c r="C21" t="n">
-        <v>22.74622041857604</v>
+        <v>31.94339759241375</v>
       </c>
       <c r="D21" t="n">
-        <v>31.94339759241375</v>
+        <v>12.21093470231118</v>
       </c>
       <c r="E21" t="n">
-        <v>12.21093470231118</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2526,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>7.226772377792192</v>
       </c>
       <c r="O21" t="n">
-        <v>7.226772377792192</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2541,65 +2484,62 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.05198665350521548</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05198665350521548</v>
+        <v>1969.978709878658</v>
       </c>
       <c r="U21" t="n">
-        <v>1969.978709878658</v>
+        <v>316.0498125581364</v>
       </c>
       <c r="V21" t="n">
-        <v>316.0498125581364</v>
+        <v>-10.21091531625622</v>
       </c>
       <c r="W21" t="n">
-        <v>-10.21091531625622</v>
+        <v>5.86883370797833</v>
       </c>
       <c r="X21" t="n">
-        <v>5.86883370797833</v>
+        <v>0.1562375522813785</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1562375522813785</v>
+        <v>7.625784978425697</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.625784978425697</v>
+        <v>1.958545681888618</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.958545681888618</v>
+        <v>9.626376899940484</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.626376907117281</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.008121921997981119</v>
-      </c>
-      <c r="AD21" t="inlineStr">
+        <v>0.008121922027125805</v>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD21" t="n">
+        <v>0.3737453520298004</v>
+      </c>
       <c r="AE21" t="n">
-        <v>3.312545537948608</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>6.985183715820312</v>
+        <v>9.997478485107422</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>700</v>
+      <c r="A22" t="n">
+        <v>24.64055238634836</v>
       </c>
       <c r="B22" t="n">
-        <v>24.64055238634836</v>
+        <v>21.25274882503955</v>
       </c>
       <c r="C22" t="n">
-        <v>21.25274882503955</v>
+        <v>27.80452469764478</v>
       </c>
       <c r="D22" t="n">
-        <v>27.80452469764478</v>
+        <v>15.57085157182014</v>
       </c>
       <c r="E22" t="n">
-        <v>15.57085157182014</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2626,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10.73132251914715</v>
       </c>
       <c r="O22" t="n">
-        <v>10.73132251914715</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2641,65 +2581,62 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.05985793982608023</v>
       </c>
       <c r="T22" t="n">
-        <v>0.05985793982608023</v>
+        <v>1996.200713394664</v>
       </c>
       <c r="U22" t="n">
-        <v>1996.200713394664</v>
+        <v>337.7521210642616</v>
       </c>
       <c r="V22" t="n">
-        <v>337.7521210642616</v>
+        <v>-12.06417246312632</v>
       </c>
       <c r="W22" t="n">
-        <v>-12.06417246312632</v>
+        <v>6.669299994840346</v>
       </c>
       <c r="X22" t="n">
-        <v>6.669299994840346</v>
+        <v>0.1714788632028532</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1714788632028532</v>
+        <v>7.361850390881773</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.361850390881773</v>
+        <v>2.03318915807749</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.03318915807749</v>
+        <v>12.83943365295199</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.83943366206022</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.001629117484999387</v>
-      </c>
-      <c r="AD22" t="inlineStr">
+        <v>0.001629117492418564</v>
+      </c>
+      <c r="AC22" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD22" t="n">
+        <v>0.2204871326684952</v>
+      </c>
       <c r="AE22" t="n">
-        <v>3.580575704574585</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>7.129753112792969</v>
+        <v>10.27313041687012</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>701</v>
+      <c r="A23" t="n">
+        <v>24.69862396067251</v>
       </c>
       <c r="B23" t="n">
-        <v>24.69862396067251</v>
+        <v>12.94677360981414</v>
       </c>
       <c r="C23" t="n">
-        <v>12.94677360981414</v>
+        <v>59.78605265772893</v>
       </c>
       <c r="D23" t="n">
-        <v>59.78605265772893</v>
+        <v>2.071458063168219</v>
       </c>
       <c r="E23" t="n">
-        <v>2.071458063168219</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2726,10 +2663,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.4970917086162015</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4970917086162015</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2741,65 +2678,62 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.01703421361986344</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01703421361986344</v>
+        <v>1829.432936207961</v>
       </c>
       <c r="U23" t="n">
-        <v>1829.432936207961</v>
+        <v>194.5359229531003</v>
       </c>
       <c r="V23" t="n">
-        <v>194.5359229531003</v>
+        <v>-4.517885222436833</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.517885222436833</v>
+        <v>2.342413511136046</v>
       </c>
       <c r="X23" t="n">
-        <v>2.342413511136046</v>
+        <v>0.09543470603399078</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.09543470603399078</v>
+        <v>8.835047045046414</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.835047045046414</v>
+        <v>1.535777422704193</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.535777422704193</v>
+        <v>23.49199440518728</v>
       </c>
       <c r="AB23" t="n">
-        <v>23.49199440103875</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.920967499908116e-06</v>
-      </c>
-      <c r="AD23" t="inlineStr">
+        <v>7.920967483476815e-06</v>
+      </c>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD23" t="n">
+        <v>-0.3167617619037628</v>
+      </c>
       <c r="AE23" t="n">
-        <v>2.55609655380249</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>5.059582233428955</v>
+        <v>7.782375812530518</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>702</v>
+      <c r="A24" t="n">
+        <v>27.11629087610016</v>
       </c>
       <c r="B24" t="n">
-        <v>27.11629087610016</v>
+        <v>14.62169899185692</v>
       </c>
       <c r="C24" t="n">
-        <v>14.62169899185692</v>
+        <v>55.25597239681475</v>
       </c>
       <c r="D24" t="n">
-        <v>55.25597239681475</v>
+        <v>2.295733512731911</v>
       </c>
       <c r="E24" t="n">
-        <v>2.295733512731911</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2826,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.7103042224962675</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7103042224962675</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2841,65 +2775,62 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.01938512517788404</v>
       </c>
       <c r="T24" t="n">
-        <v>0.01938512517788404</v>
+        <v>1841.633143209984</v>
       </c>
       <c r="U24" t="n">
-        <v>1841.633143209984</v>
+        <v>202.3816663890206</v>
       </c>
       <c r="V24" t="n">
-        <v>202.3816663890206</v>
+        <v>-4.884745617838008</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.884745617838008</v>
+        <v>2.632730186938086</v>
       </c>
       <c r="X24" t="n">
-        <v>2.632730186938086</v>
+        <v>0.09994899088701825</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.09994899088701825</v>
+        <v>8.694488378477924</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.694488378477924</v>
+        <v>1.5836150074223</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5836150074223</v>
+        <v>17.10786259373292</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.10786259006947</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.0001927857103387609</v>
-      </c>
-      <c r="AD24" t="inlineStr">
+        <v>0.000192785709985599</v>
+      </c>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD24" t="n">
+        <v>-0.2506759464740753</v>
+      </c>
       <c r="AE24" t="n">
-        <v>2.671896457672119</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>5.031870365142822</v>
+        <v>8.049174308776855</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>703</v>
+      <c r="A25" t="n">
+        <v>28.97995691733995</v>
       </c>
       <c r="B25" t="n">
-        <v>28.97995691733995</v>
+        <v>16.44395713812345</v>
       </c>
       <c r="C25" t="n">
-        <v>16.44395713812345</v>
+        <v>50.35327831911562</v>
       </c>
       <c r="D25" t="n">
-        <v>50.35327831911562</v>
+        <v>3.185006375350623</v>
       </c>
       <c r="E25" t="n">
-        <v>3.185006375350623</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2926,10 +2857,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.03780125007036</v>
       </c>
       <c r="O25" t="n">
-        <v>1.03780125007036</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2941,65 +2872,62 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.02307664646754815</v>
       </c>
       <c r="T25" t="n">
-        <v>0.02307664646754815</v>
+        <v>1859.242021620291</v>
       </c>
       <c r="U25" t="n">
-        <v>1859.242021620291</v>
+        <v>219.6686467883856</v>
       </c>
       <c r="V25" t="n">
-        <v>219.6686467883856</v>
+        <v>-5.342234570731408</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.342234570731408</v>
+        <v>2.988762674433695</v>
       </c>
       <c r="X25" t="n">
-        <v>2.988762674433695</v>
+        <v>0.1065652409568925</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1065652409568925</v>
+        <v>8.53215743748135</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.53215743748135</v>
+        <v>1.636501504486467</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.636501504486467</v>
+        <v>12.1766142525197</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.17661425759207</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.002269247208283032</v>
-      </c>
-      <c r="AD25" t="inlineStr">
+        <v>0.002269247214038206</v>
+      </c>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD25" t="n">
+        <v>-0.3184697926044464</v>
+      </c>
       <c r="AE25" t="n">
-        <v>2.687152862548828</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>5.112345218658447</v>
+        <v>8.243280410766602</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>704</v>
+      <c r="A26" t="n">
+        <v>30.34265377319738</v>
       </c>
       <c r="B26" t="n">
-        <v>30.34265377319738</v>
+        <v>17.80474339614692</v>
       </c>
       <c r="C26" t="n">
-        <v>17.80474339614692</v>
+        <v>46.34859570643516</v>
       </c>
       <c r="D26" t="n">
-        <v>46.34859570643516</v>
+        <v>4.073004266397291</v>
       </c>
       <c r="E26" t="n">
-        <v>4.073004266397291</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -3026,10 +2954,10 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.431002857823243</v>
       </c>
       <c r="O26" t="n">
-        <v>1.431002857823243</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -3041,65 +2969,62 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>0.02660818647152365</v>
       </c>
       <c r="T26" t="n">
-        <v>0.02660818647152365</v>
+        <v>1874.369014877993</v>
       </c>
       <c r="U26" t="n">
-        <v>1874.369014877993</v>
+        <v>233.7827750446807</v>
       </c>
       <c r="V26" t="n">
-        <v>233.7827750446807</v>
+        <v>-5.757498915755457</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.757498915755457</v>
+        <v>3.326658615019689</v>
       </c>
       <c r="X26" t="n">
-        <v>3.326658615019689</v>
+        <v>0.112260311158507</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.112260311158507</v>
+        <v>8.394800376906852</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.394800376906852</v>
+        <v>1.675082869941759</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.675082869941759</v>
+        <v>9.404543476465372</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.404543484323755</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.009074638428977488</v>
-      </c>
-      <c r="AD26" t="inlineStr">
+        <v>0.009074638464633411</v>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD26" t="n">
+        <v>-0.3551406264305115</v>
+      </c>
       <c r="AE26" t="n">
-        <v>2.873922348022461</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>5.238391399383545</v>
+        <v>8.375783920288086</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>705</v>
+      <c r="A27" t="n">
+        <v>31.86528713449996</v>
       </c>
       <c r="B27" t="n">
-        <v>31.86528713449996</v>
+        <v>18.23696715878395</v>
       </c>
       <c r="C27" t="n">
-        <v>18.23696715878395</v>
+        <v>42.40093148684115</v>
       </c>
       <c r="D27" t="n">
-        <v>42.40093148684115</v>
+        <v>5.290206015657255</v>
       </c>
       <c r="E27" t="n">
-        <v>5.290206015657255</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3126,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.206608204217674</v>
       </c>
       <c r="O27" t="n">
-        <v>2.206608204217674</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -3141,65 +3066,62 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.03193803030454426</v>
       </c>
       <c r="T27" t="n">
-        <v>0.03193803030454426</v>
+        <v>1888.522296876517</v>
       </c>
       <c r="U27" t="n">
-        <v>1888.522296876517</v>
+        <v>248.7015154097846</v>
       </c>
       <c r="V27" t="n">
-        <v>248.7015154097846</v>
+        <v>-6.405330687502009</v>
       </c>
       <c r="W27" t="n">
-        <v>-6.405330687502009</v>
+        <v>3.86801246377312</v>
       </c>
       <c r="X27" t="n">
-        <v>3.86801246377312</v>
+        <v>0.1188191128917422</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1188191128917422</v>
+        <v>8.257133996825495</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.257133996825495</v>
+        <v>1.715493650301267</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.715493650301267</v>
+        <v>7.549824680494376</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.549824684860257</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.02293910133967969</v>
-      </c>
-      <c r="AD27" t="inlineStr">
+        <v>0.02293910138975441</v>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD27" t="n">
+        <v>-0.2471255213022232</v>
+      </c>
       <c r="AE27" t="n">
-        <v>3.17240834236145</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>5.770833015441895</v>
+        <v>9.023309707641602</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>706</v>
+      <c r="A28" t="n">
+        <v>31.70139237157215</v>
       </c>
       <c r="B28" t="n">
-        <v>31.70139237157215</v>
+        <v>19.10423570636226</v>
       </c>
       <c r="C28" t="n">
-        <v>19.10423570636226</v>
+        <v>38.63291780669091</v>
       </c>
       <c r="D28" t="n">
-        <v>38.63291780669091</v>
+        <v>7.016579441970052</v>
       </c>
       <c r="E28" t="n">
-        <v>7.016579441970052</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3226,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.544874673404641</v>
       </c>
       <c r="O28" t="n">
-        <v>3.544874673404641</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3241,65 +3163,62 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.03889647897676301</v>
       </c>
       <c r="T28" t="n">
-        <v>0.03889647897676301</v>
+        <v>1908.625083921418</v>
       </c>
       <c r="U28" t="n">
-        <v>1908.625083921418</v>
+        <v>268.3262209995152</v>
       </c>
       <c r="V28" t="n">
-        <v>268.3262209995152</v>
+        <v>-7.528630542893998</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.528630542893998</v>
+        <v>4.589834679450541</v>
       </c>
       <c r="X28" t="n">
-        <v>4.589834679450541</v>
+        <v>0.1290665430053385</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1290665430053385</v>
+        <v>8.079933631752704</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.079933631752704</v>
+        <v>1.788739041612613</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.788739041612613</v>
+        <v>6.904061772511194</v>
       </c>
       <c r="AB28" t="n">
-        <v>6.904061780739121</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.03168122989426314</v>
-      </c>
-      <c r="AD28" t="inlineStr">
+        <v>0.03168123002459855</v>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD28" t="n">
+        <v>-0.1747732013463974</v>
+      </c>
       <c r="AE28" t="n">
-        <v>3.439621686935425</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>6.1625657081604</v>
+        <v>9.459661483764648</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>707</v>
+      <c r="A29" t="n">
+        <v>31.7420363140709</v>
       </c>
       <c r="B29" t="n">
-        <v>31.7420363140709</v>
+        <v>19.34137208626396</v>
       </c>
       <c r="C29" t="n">
-        <v>19.34137208626396</v>
+        <v>35.29946336459976</v>
       </c>
       <c r="D29" t="n">
-        <v>35.29946336459976</v>
+        <v>8.488290469014574</v>
       </c>
       <c r="E29" t="n">
-        <v>8.488290469014574</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -3326,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.128837766050812</v>
       </c>
       <c r="O29" t="n">
-        <v>5.128837766050812</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3341,65 +3260,62 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.04509242286438607</v>
       </c>
       <c r="T29" t="n">
-        <v>0.04509242286438607</v>
+        <v>1924.534454712694</v>
       </c>
       <c r="U29" t="n">
-        <v>1924.534454712694</v>
+        <v>282.1894380959296</v>
       </c>
       <c r="V29" t="n">
-        <v>282.1894380959296</v>
+        <v>-8.668713231012978</v>
       </c>
       <c r="W29" t="n">
-        <v>-8.668713231012978</v>
+        <v>5.222827047467528</v>
       </c>
       <c r="X29" t="n">
-        <v>5.222827047467528</v>
+        <v>0.1379805743975732</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1379805743975732</v>
+        <v>7.915605804901404</v>
       </c>
       <c r="Z29" t="n">
-        <v>7.915605804901404</v>
+        <v>1.850493355719852</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.850493355719852</v>
+        <v>7.136372049725259</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.136372054400284</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.02820697398443595</v>
-      </c>
-      <c r="AD29" t="inlineStr">
+        <v>0.02820697405037009</v>
+      </c>
+      <c r="AC29" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD29" t="n">
+        <v>-0.001511362614110112</v>
+      </c>
       <c r="AE29" t="n">
-        <v>3.460787773132324</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>6.677536010742188</v>
+        <v>9.749970436096191</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>708</v>
+      <c r="A30" t="n">
+        <v>30.76237588603813</v>
       </c>
       <c r="B30" t="n">
-        <v>30.76237588603813</v>
+        <v>18.31664101925855</v>
       </c>
       <c r="C30" t="n">
-        <v>18.31664101925855</v>
+        <v>32.12872020698693</v>
       </c>
       <c r="D30" t="n">
-        <v>32.12872020698693</v>
+        <v>11.0502077792672</v>
       </c>
       <c r="E30" t="n">
-        <v>11.0502077792672</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3426,10 +3342,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>7.742055108449174</v>
       </c>
       <c r="O30" t="n">
-        <v>7.742055108449174</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3441,65 +3357,62 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>0.05304218528784226</v>
       </c>
       <c r="T30" t="n">
-        <v>0.05304218528784226</v>
+        <v>1944.45525054741</v>
       </c>
       <c r="U30" t="n">
-        <v>1944.45525054741</v>
+        <v>303.655158994235</v>
       </c>
       <c r="V30" t="n">
-        <v>303.655158994235</v>
+        <v>-10.45824427832613</v>
       </c>
       <c r="W30" t="n">
-        <v>-10.45824427832613</v>
+        <v>6.059471159808631</v>
       </c>
       <c r="X30" t="n">
-        <v>6.059471159808631</v>
+        <v>0.1511517078432263</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1511517078432263</v>
+        <v>7.718060858733408</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.718060858733408</v>
+        <v>1.941272622660873</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.941272622660873</v>
+        <v>8.687525801432193</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.687525801772399</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.0129875652191106</v>
-      </c>
-      <c r="AD30" t="inlineStr">
+        <v>0.01298756522131983</v>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD30" t="n">
+        <v>0.1991914063692093</v>
+      </c>
       <c r="AE30" t="n">
-        <v>3.591811656951904</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>6.987906932830811</v>
+        <v>10.12330627441406</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>709</v>
+      <c r="A31" t="n">
+        <v>29.73442789455431</v>
       </c>
       <c r="B31" t="n">
-        <v>29.73442789455431</v>
+        <v>17.25824278002907</v>
       </c>
       <c r="C31" t="n">
-        <v>17.25824278002907</v>
+        <v>28.51150635643484</v>
       </c>
       <c r="D31" t="n">
-        <v>28.51150635643484</v>
+        <v>12.65461180418959</v>
       </c>
       <c r="E31" t="n">
-        <v>12.65461180418959</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -3526,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>11.8412111647922</v>
       </c>
       <c r="O31" t="n">
-        <v>11.8412111647922</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3541,65 +3454,62 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.06136890664099688</v>
       </c>
       <c r="T31" t="n">
-        <v>0.06136890664099688</v>
+        <v>1959.846181129472</v>
       </c>
       <c r="U31" t="n">
-        <v>1959.846181129472</v>
+        <v>313.2213556904683</v>
       </c>
       <c r="V31" t="n">
-        <v>313.2213556904683</v>
+        <v>-12.78837389426011</v>
       </c>
       <c r="W31" t="n">
-        <v>-12.78837389426011</v>
+        <v>6.949359547274402</v>
       </c>
       <c r="X31" t="n">
-        <v>6.949359547274402</v>
+        <v>0.1642509978251735</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1642509978251735</v>
+        <v>7.453239485040992</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.453239485040992</v>
+        <v>2.045982747978778</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.045982747978778</v>
+        <v>11.6344926948951</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.63449269756732</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.002975788155705761</v>
-      </c>
-      <c r="AD31" t="inlineStr">
+        <v>0.002975788159681803</v>
+      </c>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD31" t="n">
+        <v>0.08492428064346313</v>
+      </c>
       <c r="AE31" t="n">
-        <v>3.774492979049683</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>7.208007335662842</v>
+        <v>10.3868293762207</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>710</v>
+      <c r="A32" t="n">
+        <v>30.37782838567884</v>
       </c>
       <c r="B32" t="n">
-        <v>30.37782838567884</v>
+        <v>9.609360149062256</v>
       </c>
       <c r="C32" t="n">
-        <v>9.609360149062256</v>
+        <v>57.91933065856235</v>
       </c>
       <c r="D32" t="n">
-        <v>57.91933065856235</v>
+        <v>1.589063142119515</v>
       </c>
       <c r="E32" t="n">
-        <v>1.589063142119515</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3626,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.5044176645770377</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5044176645770377</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -3641,65 +3551,62 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.01642425646165967</v>
       </c>
       <c r="T32" t="n">
-        <v>0.01642425646165967</v>
+        <v>1814.229384283334</v>
       </c>
       <c r="U32" t="n">
-        <v>1814.229384283334</v>
+        <v>172.1043267389533</v>
       </c>
       <c r="V32" t="n">
-        <v>172.1043267389533</v>
+        <v>-4.028868396605834</v>
       </c>
       <c r="W32" t="n">
-        <v>-4.028868396605834</v>
+        <v>2.290221615134703</v>
       </c>
       <c r="X32" t="n">
-        <v>2.290221615134703</v>
+        <v>0.08608831927901155</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.08608831927901155</v>
+        <v>8.877229809856253</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.877229809856253</v>
+        <v>1.433340635221596</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.433340635221596</v>
+        <v>21.69013716335309</v>
       </c>
       <c r="AB32" t="n">
-        <v>21.69013717077402</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.950053639399041e-05</v>
-      </c>
-      <c r="AD32" t="inlineStr">
+        <v>1.950053646637695e-05</v>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD32" t="n">
+        <v>-0.6439177393913269</v>
+      </c>
       <c r="AE32" t="n">
-        <v>2.998231172561646</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>4.997187614440918</v>
+        <v>7.902314186096191</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>711</v>
+      <c r="A33" t="n">
+        <v>33.11659379389907</v>
       </c>
       <c r="B33" t="n">
-        <v>33.11659379389907</v>
+        <v>10.973333777346</v>
       </c>
       <c r="C33" t="n">
-        <v>10.973333777346</v>
+        <v>52.9251697901506</v>
       </c>
       <c r="D33" t="n">
-        <v>52.9251697901506</v>
+        <v>2.192065154734242</v>
       </c>
       <c r="E33" t="n">
-        <v>2.192065154734242</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3726,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.7928374838700868</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7928374838700868</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3741,65 +3648,62 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>0.02005287698639602</v>
       </c>
       <c r="T33" t="n">
-        <v>0.02005287698639602</v>
+        <v>1828.174076480354</v>
       </c>
       <c r="U33" t="n">
-        <v>1828.174076480354</v>
+        <v>187.8867026100067</v>
       </c>
       <c r="V33" t="n">
-        <v>187.8867026100067</v>
+        <v>-4.483383626027237</v>
       </c>
       <c r="W33" t="n">
-        <v>-4.483383626027237</v>
+        <v>2.675542255443848</v>
       </c>
       <c r="X33" t="n">
-        <v>2.675542255443848</v>
+        <v>0.0923369200142214</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0923369200142214</v>
+        <v>8.727387485378394</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.727387485378394</v>
+        <v>1.49184845250026</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.49184845250026</v>
+        <v>15.3220351611041</v>
       </c>
       <c r="AB33" t="n">
-        <v>15.3220351635599</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.0004708280608920479</v>
-      </c>
-      <c r="AD33" t="inlineStr">
+        <v>0.000470828061470141</v>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD33" t="n">
+        <v>-0.6051358580589294</v>
+      </c>
       <c r="AE33" t="n">
-        <v>3.113670825958252</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>4.988369941711426</v>
+        <v>8.239546775817871</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>712</v>
+      <c r="A34" t="n">
+        <v>35.40504769440309</v>
       </c>
       <c r="B34" t="n">
-        <v>35.40504769440309</v>
+        <v>12.25967062301765</v>
       </c>
       <c r="C34" t="n">
-        <v>12.25967062301765</v>
+        <v>48.28190961500265</v>
       </c>
       <c r="D34" t="n">
-        <v>48.28190961500265</v>
+        <v>2.949080621569796</v>
       </c>
       <c r="E34" t="n">
-        <v>2.949080621569796</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3826,10 +3730,10 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.104291446006826</v>
       </c>
       <c r="O34" t="n">
-        <v>1.104291446006826</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3841,65 +3745,62 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.02340667151348477</v>
       </c>
       <c r="T34" t="n">
-        <v>0.02340667151348477</v>
+        <v>1842.53899141852</v>
       </c>
       <c r="U34" t="n">
-        <v>1842.53899141852</v>
+        <v>203.9119805416204</v>
       </c>
       <c r="V34" t="n">
-        <v>203.9119805416204</v>
+        <v>-4.879964777771954</v>
       </c>
       <c r="W34" t="n">
-        <v>-4.879964777771954</v>
+        <v>2.9914260627542</v>
       </c>
       <c r="X34" t="n">
-        <v>2.9914260627542</v>
+        <v>0.09831534675329141</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.09831534675329141</v>
+        <v>8.584083714612751</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.584083714612751</v>
+        <v>1.537891595222004</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.537891595222004</v>
+        <v>11.21058081833331</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.21058081905238</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.003678352160619291</v>
-      </c>
-      <c r="AD34" t="inlineStr">
+        <v>0.003678352161941789</v>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD34" t="n">
+        <v>-0.6616136431694031</v>
+      </c>
       <c r="AE34" t="n">
-        <v>3.221651315689087</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>5.175657272338867</v>
+        <v>8.527173042297363</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>713</v>
+      <c r="A35" t="n">
+        <v>37.57764389518124</v>
       </c>
       <c r="B35" t="n">
-        <v>37.57764389518124</v>
+        <v>12.9045729319361</v>
       </c>
       <c r="C35" t="n">
-        <v>12.9045729319361</v>
+        <v>44.21310951760462</v>
       </c>
       <c r="D35" t="n">
-        <v>44.21310951760462</v>
+        <v>3.638680888316341</v>
       </c>
       <c r="E35" t="n">
-        <v>3.638680888316341</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3926,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.665992766961695</v>
       </c>
       <c r="O35" t="n">
-        <v>1.665992766961695</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3941,65 +3842,62 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.02778607059658024</v>
       </c>
       <c r="T35" t="n">
-        <v>0.02778607059658024</v>
+        <v>1853.772168131376</v>
       </c>
       <c r="U35" t="n">
-        <v>1853.772168131376</v>
+        <v>215.3435763930484</v>
       </c>
       <c r="V35" t="n">
-        <v>215.3435763930484</v>
+        <v>-5.401715275000322</v>
       </c>
       <c r="W35" t="n">
-        <v>-5.401715275000322</v>
+        <v>3.451649138168169</v>
       </c>
       <c r="X35" t="n">
-        <v>3.451649138168169</v>
+        <v>0.1037615697629466</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1037615697629466</v>
+        <v>8.455130350823579</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.455130350823579</v>
+        <v>1.578391418888722</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.578391418888722</v>
+        <v>8.99492199951454</v>
       </c>
       <c r="AB35" t="n">
-        <v>8.994921998980134</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.01113723812364598</v>
-      </c>
-      <c r="AD35" t="inlineStr">
+        <v>0.01113723812067002</v>
+      </c>
+      <c r="AC35" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD35" t="n">
+        <v>-0.5920065641403198</v>
+      </c>
       <c r="AE35" t="n">
-        <v>3.387543916702271</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>5.409714698791504</v>
+        <v>8.761042594909668</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>714</v>
+      <c r="A36" t="n">
+        <v>38.09115608907656</v>
       </c>
       <c r="B36" t="n">
-        <v>38.09115608907656</v>
+        <v>14.24077169642902</v>
       </c>
       <c r="C36" t="n">
-        <v>14.24077169642902</v>
+        <v>40.34117942701062</v>
       </c>
       <c r="D36" t="n">
-        <v>40.34117942701062</v>
+        <v>4.820091728927136</v>
       </c>
       <c r="E36" t="n">
-        <v>4.820091728927136</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -4026,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.50680105855667</v>
       </c>
       <c r="O36" t="n">
-        <v>2.50680105855667</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -4041,65 +3939,62 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.03320309666656895</v>
       </c>
       <c r="T36" t="n">
-        <v>0.03320309666656895</v>
+        <v>1871.328810638551</v>
       </c>
       <c r="U36" t="n">
-        <v>1871.328810638551</v>
+        <v>234.1195505358265</v>
       </c>
       <c r="V36" t="n">
-        <v>234.1195505358265</v>
+        <v>-6.20754810295613</v>
       </c>
       <c r="W36" t="n">
-        <v>-6.20754810295613</v>
+        <v>3.995672476732513</v>
       </c>
       <c r="X36" t="n">
-        <v>3.995672476732513</v>
+        <v>0.1125949163041201</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.1125949163041201</v>
+        <v>8.296085052838539</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.296085052838539</v>
+        <v>1.646076820663437</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.646076820663437</v>
+        <v>7.589695240298815</v>
       </c>
       <c r="AB36" t="n">
-        <v>7.589695238513221</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.02248633203967598</v>
-      </c>
-      <c r="AD36" t="inlineStr">
+        <v>0.02248633201960026</v>
+      </c>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD36" t="n">
+        <v>-0.520613431930542</v>
+      </c>
       <c r="AE36" t="n">
-        <v>3.560274600982666</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>5.728890419006348</v>
+        <v>9.138334274291992</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>715</v>
+      <c r="A37" t="n">
+        <v>38.33579750611559</v>
       </c>
       <c r="B37" t="n">
-        <v>38.33579750611559</v>
+        <v>14.22310473337481</v>
       </c>
       <c r="C37" t="n">
-        <v>14.22310473337481</v>
+        <v>37.73458860799308</v>
       </c>
       <c r="D37" t="n">
-        <v>37.73458860799308</v>
+        <v>6.084502628677954</v>
       </c>
       <c r="E37" t="n">
-        <v>6.084502628677954</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -4126,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.622006523838574</v>
       </c>
       <c r="O37" t="n">
-        <v>3.622006523838574</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -4141,65 +4036,62 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.03884687487624496</v>
       </c>
       <c r="T37" t="n">
-        <v>0.03884687487624496</v>
+        <v>1883.454069982317</v>
       </c>
       <c r="U37" t="n">
-        <v>1883.454069982317</v>
+        <v>249.5231895669747</v>
       </c>
       <c r="V37" t="n">
-        <v>249.5231895669747</v>
+        <v>-7.149269888331517</v>
       </c>
       <c r="W37" t="n">
-        <v>-7.149269888331517</v>
+        <v>4.580602116731223</v>
       </c>
       <c r="X37" t="n">
-        <v>4.580602116731223</v>
+        <v>0.1204672738191375</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1204672738191375</v>
+        <v>8.177522697748598</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.177522697748598</v>
+        <v>1.706887303940507</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.706887303940507</v>
+        <v>7.482550757770128</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.482550757700241</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.02372382696146502</v>
-      </c>
-      <c r="AD37" t="inlineStr">
+        <v>0.02372382696063602</v>
+      </c>
+      <c r="AC37" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD37" t="n">
+        <v>-0.4234223663806915</v>
+      </c>
       <c r="AE37" t="n">
-        <v>3.763417720794678</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>6.141497135162354</v>
+        <v>9.547578811645508</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>716</v>
+      <c r="A38" t="n">
+        <v>37.89528654115976</v>
       </c>
       <c r="B38" t="n">
-        <v>37.89528654115976</v>
+        <v>15.01810551709215</v>
       </c>
       <c r="C38" t="n">
-        <v>15.01810551709215</v>
+        <v>34.00711535766091</v>
       </c>
       <c r="D38" t="n">
-        <v>34.00711535766091</v>
+        <v>7.695501594568473</v>
       </c>
       <c r="E38" t="n">
-        <v>7.695501594568473</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -4226,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.383990989518713</v>
       </c>
       <c r="O38" t="n">
-        <v>5.383990989518713</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -4241,65 +4133,62 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.04571517909500261</v>
       </c>
       <c r="T38" t="n">
-        <v>0.04571517909500261</v>
+        <v>1903.055727052831</v>
       </c>
       <c r="U38" t="n">
-        <v>1903.055727052831</v>
+        <v>267.955517596444</v>
       </c>
       <c r="V38" t="n">
-        <v>267.955517596444</v>
+        <v>-8.499983747448454</v>
       </c>
       <c r="W38" t="n">
-        <v>-8.499983747448454</v>
+        <v>5.257125421822825</v>
       </c>
       <c r="X38" t="n">
-        <v>5.257125421822825</v>
+        <v>0.1317698614362234</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1317698614362234</v>
+        <v>7.983231044902072</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.983231044902072</v>
+        <v>1.793112124583807</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.793112124583807</v>
+        <v>7.750979712769805</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.750979713683767</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.02074417370898962</v>
-      </c>
-      <c r="AD38" t="inlineStr">
+        <v>0.02074417371846926</v>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD38" t="n">
+        <v>-0.2380699515342712</v>
+      </c>
       <c r="AE38" t="n">
-        <v>3.755874156951904</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>6.494069576263428</v>
+        <v>9.954304695129395</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>717</v>
+      <c r="A39" t="n">
+        <v>37.04916938976096</v>
       </c>
       <c r="B39" t="n">
-        <v>37.04916938976096</v>
+        <v>14.93908228947561</v>
       </c>
       <c r="C39" t="n">
-        <v>14.93908228947561</v>
+        <v>31.37594742238257</v>
       </c>
       <c r="D39" t="n">
-        <v>31.37594742238257</v>
+        <v>8.703754693933551</v>
       </c>
       <c r="E39" t="n">
-        <v>8.703754693933551</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -4326,10 +4215,10 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.93204620444731</v>
       </c>
       <c r="O39" t="n">
-        <v>7.93204620444731</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -4341,65 +4230,62 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.05292177768615149</v>
       </c>
       <c r="T39" t="n">
-        <v>0.05292177768615149</v>
+        <v>1915.270699666103</v>
       </c>
       <c r="U39" t="n">
-        <v>1915.270699666103</v>
+        <v>276.8059324216907</v>
       </c>
       <c r="V39" t="n">
-        <v>276.8059324216907</v>
+        <v>-10.28152875885367</v>
       </c>
       <c r="W39" t="n">
-        <v>-10.28152875885367</v>
+        <v>6.021516298486138</v>
       </c>
       <c r="X39" t="n">
-        <v>6.021516298486138</v>
+        <v>0.1421670544178495</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.1421670544178495</v>
+        <v>7.799204875257918</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.799204875257918</v>
+        <v>1.891498966762572</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.891498966762572</v>
+        <v>8.845619707477619</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.845619704925543</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.01200046532979826</v>
-      </c>
-      <c r="AD39" t="inlineStr">
+        <v>0.01200046531448529</v>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD39" t="n">
+        <v>-0.1230912208557129</v>
+      </c>
       <c r="AE39" t="n">
-        <v>3.822630405426025</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>6.76807975769043</v>
+        <v>10.0349645614624</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>718</v>
+      <c r="A40" t="n">
+        <v>35.00856026880581</v>
       </c>
       <c r="B40" t="n">
-        <v>35.00856026880581</v>
+        <v>13.49101090758822</v>
       </c>
       <c r="C40" t="n">
-        <v>13.49101090758822</v>
+        <v>28.41328965570146</v>
       </c>
       <c r="D40" t="n">
-        <v>28.41328965570146</v>
+        <v>10.74232139561721</v>
       </c>
       <c r="E40" t="n">
-        <v>10.74232139561721</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -4426,10 +4312,10 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>12.34481777228729</v>
       </c>
       <c r="O40" t="n">
-        <v>12.34481777228729</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -4441,65 +4327,62 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>0.06203850431051611</v>
       </c>
       <c r="T40" t="n">
-        <v>0.06203850431051611</v>
+        <v>1931.991337486817</v>
       </c>
       <c r="U40" t="n">
-        <v>1931.991337486817</v>
+        <v>292.9426643223443</v>
       </c>
       <c r="V40" t="n">
-        <v>292.9426643223443</v>
+        <v>-13.03630535919964</v>
       </c>
       <c r="W40" t="n">
-        <v>-13.03630535919964</v>
+        <v>6.993463708553959</v>
       </c>
       <c r="X40" t="n">
-        <v>6.993463708553959</v>
+        <v>0.1579263444042211</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1579263444042211</v>
+        <v>7.536729373264516</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.536729373264516</v>
+        <v>2.030469900039257</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.030469900039257</v>
+        <v>12.01846226477663</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.01846226109998</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.002455975779409036</v>
-      </c>
-      <c r="AD40" t="inlineStr">
+        <v>0.002455975774894203</v>
+      </c>
+      <c r="AC40" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD40" t="n">
+        <v>-0.0612655021250248</v>
+      </c>
       <c r="AE40" t="n">
-        <v>3.893937110900879</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>6.991714000701904</v>
+        <v>10.39789485931396</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>719</v>
+      <c r="A41" t="n">
+        <v>37.58863922492247</v>
       </c>
       <c r="B41" t="n">
-        <v>37.58863922492247</v>
+        <v>7.280669539785599</v>
       </c>
       <c r="C41" t="n">
-        <v>7.280669539785599</v>
+        <v>53.11798962683208</v>
       </c>
       <c r="D41" t="n">
-        <v>53.11798962683208</v>
+        <v>1.532428398584247</v>
       </c>
       <c r="E41" t="n">
-        <v>1.532428398584247</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -4526,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.4802732098756072</v>
       </c>
       <c r="O41" t="n">
-        <v>0.4802732098756072</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -4541,65 +4424,62 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.01611792915068352</v>
       </c>
       <c r="T41" t="n">
-        <v>0.01611792915068352</v>
+        <v>1808.239641107628</v>
       </c>
       <c r="U41" t="n">
-        <v>1808.239641107628</v>
+        <v>159.2970297831138</v>
       </c>
       <c r="V41" t="n">
-        <v>159.2970297831138</v>
+        <v>-3.636299676179426</v>
       </c>
       <c r="W41" t="n">
-        <v>-3.636299676179426</v>
+        <v>2.152628046095119</v>
       </c>
       <c r="X41" t="n">
-        <v>2.152628046095119</v>
+        <v>0.07917362595361378</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.07917362595361378</v>
+        <v>8.835891679616507</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.835891679616507</v>
+        <v>1.3515369856457</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.3515369856457</v>
+        <v>18.11110486256806</v>
       </c>
       <c r="AB41" t="n">
-        <v>18.11110485649575</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.0001167410378163369</v>
-      </c>
-      <c r="AD41" t="inlineStr">
+        <v>0.0001167410374618427</v>
+      </c>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD41" t="n">
+        <v>-0.7861391305923462</v>
+      </c>
       <c r="AE41" t="n">
-        <v>3.272864818572998</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>5.054690837860107</v>
+        <v>8.172677993774414</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>720</v>
+      <c r="A42" t="n">
+        <v>40.4685427958547</v>
       </c>
       <c r="B42" t="n">
-        <v>40.4685427958547</v>
+        <v>8.207754828513329</v>
       </c>
       <c r="C42" t="n">
-        <v>8.207754828513329</v>
+        <v>48.6819596677876</v>
       </c>
       <c r="D42" t="n">
-        <v>48.6819596677876</v>
+        <v>1.960066248394547</v>
       </c>
       <c r="E42" t="n">
-        <v>1.960066248394547</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -4626,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.6816764594498212</v>
       </c>
       <c r="O42" t="n">
-        <v>0.6816764594498212</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -4641,65 +4521,62 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.01880086586279406</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01880086586279406</v>
+        <v>1818.68382189645</v>
       </c>
       <c r="U42" t="n">
-        <v>1818.68382189645</v>
+        <v>171.5358855826844</v>
       </c>
       <c r="V42" t="n">
-        <v>171.5358855826844</v>
+        <v>-3.916494663786127</v>
       </c>
       <c r="W42" t="n">
-        <v>-3.916494663786127</v>
+        <v>2.421695666149761</v>
       </c>
       <c r="X42" t="n">
-        <v>2.421695666149761</v>
+        <v>0.08383711990900984</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.08383711990900984</v>
+        <v>8.713002271277935</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.713002271277935</v>
+        <v>1.389207621495003</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.389207621495003</v>
+        <v>14.2013121199662</v>
       </c>
       <c r="AB42" t="n">
-        <v>14.20131210971228</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.0008245637867012601</v>
-      </c>
-      <c r="AD42" t="inlineStr">
+        <v>0.0008245637824737528</v>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD42" t="n">
+        <v>-0.9169075489044189</v>
+      </c>
       <c r="AE42" t="n">
-        <v>3.546592712402344</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>5.057745933532715</v>
+        <v>8.407810211181641</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>721</v>
+      <c r="A43" t="n">
+        <v>42.41365999634309</v>
       </c>
       <c r="B43" t="n">
-        <v>42.41365999634309</v>
+        <v>8.999093989015684</v>
       </c>
       <c r="C43" t="n">
-        <v>8.999093989015684</v>
+        <v>45.39868393715567</v>
       </c>
       <c r="D43" t="n">
-        <v>45.39868393715567</v>
+        <v>2.232970990007884</v>
       </c>
       <c r="E43" t="n">
-        <v>2.232970990007884</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -4726,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>0.9555910874776881</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9555910874776881</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -4741,65 +4618,62 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.02152349612150524</v>
       </c>
       <c r="T43" t="n">
-        <v>0.02152349612150524</v>
+        <v>1826.726076183138</v>
       </c>
       <c r="U43" t="n">
-        <v>1826.726076183138</v>
+        <v>179.2341687858081</v>
       </c>
       <c r="V43" t="n">
-        <v>179.2341687858081</v>
+        <v>-4.220984231619052</v>
       </c>
       <c r="W43" t="n">
-        <v>-4.220984231619052</v>
+        <v>2.725126528949924</v>
       </c>
       <c r="X43" t="n">
-        <v>2.725126528949924</v>
+        <v>0.08781957068462755</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.08781957068462755</v>
+        <v>8.614216723080775</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.614216723080775</v>
+        <v>1.422324757136511</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.422324757136511</v>
+        <v>12.18487652613888</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.18487652516843</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.002259891981618467</v>
-      </c>
-      <c r="AD43" t="inlineStr">
+        <v>0.002259891980522011</v>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD43" t="n">
+        <v>-0.9481620192527771</v>
+      </c>
       <c r="AE43" t="n">
-        <v>3.621646642684937</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>5.138691425323486</v>
+        <v>8.501886367797852</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>722</v>
+      <c r="A44" t="n">
+        <v>44.05056700894834</v>
       </c>
       <c r="B44" t="n">
-        <v>44.05056700894834</v>
+        <v>9.890677495893094</v>
       </c>
       <c r="C44" t="n">
-        <v>9.890677495893094</v>
+        <v>40.9711385049328</v>
       </c>
       <c r="D44" t="n">
-        <v>40.9711385049328</v>
+        <v>3.582962479712098</v>
       </c>
       <c r="E44" t="n">
-        <v>3.582962479712098</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4826,10 +4700,10 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.504654510513664</v>
       </c>
       <c r="O44" t="n">
-        <v>1.504654510513664</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -4841,65 +4715,62 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>0.02682561572720428</v>
       </c>
       <c r="T44" t="n">
-        <v>0.02682561572720428</v>
+        <v>1843.565591080131</v>
       </c>
       <c r="U44" t="n">
-        <v>1843.565591080131</v>
+        <v>204.9714206893031</v>
       </c>
       <c r="V44" t="n">
-        <v>204.9714206893031</v>
+        <v>-4.800828487715472</v>
       </c>
       <c r="W44" t="n">
-        <v>-4.800828487715472</v>
+        <v>3.208694179126411</v>
       </c>
       <c r="X44" t="n">
-        <v>3.208694179126411</v>
+        <v>0.0965251354987447</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.0965251354987447</v>
+        <v>8.466966945027915</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.466966945027915</v>
+        <v>1.480117606964709</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.480117606964709</v>
+        <v>10.40686087518002</v>
       </c>
       <c r="AB44" t="n">
-        <v>10.40686087148101</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.005497672623082317</v>
-      </c>
-      <c r="AD44" t="inlineStr">
+        <v>0.005497672612914339</v>
+      </c>
+      <c r="AC44" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD44" t="n">
+        <v>-0.9625558853149414</v>
+      </c>
       <c r="AE44" t="n">
-        <v>3.852691888809204</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>5.393496513366699</v>
+        <v>8.990345001220703</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>723</v>
+      <c r="A45" t="n">
+        <v>45.28527361475503</v>
       </c>
       <c r="B45" t="n">
-        <v>45.28527361475503</v>
+        <v>10.45016941021403</v>
       </c>
       <c r="C45" t="n">
-        <v>10.45016941021403</v>
+        <v>38.05554080101164</v>
       </c>
       <c r="D45" t="n">
-        <v>38.05554080101164</v>
+        <v>4.05760531167356</v>
       </c>
       <c r="E45" t="n">
-        <v>4.05760531167356</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4926,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.151410862345743</v>
       </c>
       <c r="O45" t="n">
-        <v>2.151410862345743</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4941,65 +4812,62 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>0.03095282062176732</v>
       </c>
       <c r="T45" t="n">
-        <v>0.03095282062176732</v>
+        <v>1852.242822712511</v>
       </c>
       <c r="U45" t="n">
-        <v>1852.242822712511</v>
+        <v>213.1614044856885</v>
       </c>
       <c r="V45" t="n">
-        <v>213.1614044856885</v>
+        <v>-5.367300049169668</v>
       </c>
       <c r="W45" t="n">
-        <v>-5.367300049169668</v>
+        <v>3.649523120293471</v>
       </c>
       <c r="X45" t="n">
-        <v>3.649523120293471</v>
+        <v>0.1018977667132576</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1018977667132576</v>
+        <v>8.360768390150598</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.360768390150598</v>
+        <v>1.523919880415215</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.523919880415215</v>
+        <v>10.02177617185081</v>
       </c>
       <c r="AB45" t="n">
-        <v>10.02177617556086</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.006664981588436425</v>
-      </c>
-      <c r="AD45" t="inlineStr">
+        <v>0.006664981600800091</v>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD45" t="n">
+        <v>-0.9071553945541382</v>
+      </c>
       <c r="AE45" t="n">
-        <v>3.978915691375732</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>5.678436756134033</v>
+        <v>9.194972991943359</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>724</v>
+      <c r="A46" t="n">
+        <v>45.11415223222625</v>
       </c>
       <c r="B46" t="n">
-        <v>45.11415223222625</v>
+        <v>10.88678210520005</v>
       </c>
       <c r="C46" t="n">
-        <v>10.88678210520005</v>
+        <v>35.43340443761144</v>
       </c>
       <c r="D46" t="n">
-        <v>35.43340443761144</v>
+        <v>5.105603303705024</v>
       </c>
       <c r="E46" t="n">
-        <v>5.105603303705024</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -5026,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.460057921257236</v>
       </c>
       <c r="O46" t="n">
-        <v>3.460057921257236</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -5041,65 +4909,62 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.03774512712960618</v>
       </c>
       <c r="T46" t="n">
-        <v>0.03774512712960618</v>
+        <v>1864.986554005233</v>
       </c>
       <c r="U46" t="n">
-        <v>1864.986554005233</v>
+        <v>228.820640115054</v>
       </c>
       <c r="V46" t="n">
-        <v>228.820640115054</v>
+        <v>-6.533251677848139</v>
       </c>
       <c r="W46" t="n">
-        <v>-6.533251677848139</v>
+        <v>4.375147715580694</v>
       </c>
       <c r="X46" t="n">
-        <v>4.375147715580694</v>
+        <v>0.1115694150144273</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1115694150144273</v>
+        <v>8.225087575242839</v>
       </c>
       <c r="Z46" t="n">
-        <v>8.225087575242839</v>
+        <v>1.611128225553049</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.611128225553049</v>
+        <v>9.815023754314485</v>
       </c>
       <c r="AB46" t="n">
-        <v>9.815023754633067</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.007390854826390125</v>
-      </c>
-      <c r="AD46" t="inlineStr">
+        <v>0.007390854827567406</v>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD46" t="n">
+        <v>-0.800586462020874</v>
+      </c>
       <c r="AE46" t="n">
-        <v>4.120884418487549</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>5.975300788879395</v>
+        <v>9.540180206298828</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>725</v>
+      <c r="A47" t="n">
+        <v>44.97584185956661</v>
       </c>
       <c r="B47" t="n">
-        <v>44.97584185956661</v>
+        <v>11.26384164075777</v>
       </c>
       <c r="C47" t="n">
-        <v>11.26384164075777</v>
+        <v>32.0942836230312</v>
       </c>
       <c r="D47" t="n">
-        <v>32.0942836230312</v>
+        <v>6.302047026935472</v>
       </c>
       <c r="E47" t="n">
-        <v>6.302047026935472</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -5126,10 +4991,10 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>5.363985849708929</v>
       </c>
       <c r="O47" t="n">
-        <v>5.363985849708929</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -5141,65 +5006,62 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>0.04519229896075171</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04519229896075171</v>
+        <v>1879.925142298614</v>
       </c>
       <c r="U47" t="n">
-        <v>1879.925142298614</v>
+        <v>244.2319599421378</v>
       </c>
       <c r="V47" t="n">
-        <v>244.2319599421378</v>
+        <v>-8.024936354289267</v>
       </c>
       <c r="W47" t="n">
-        <v>-8.024936354289267</v>
+        <v>5.108179535392596</v>
       </c>
       <c r="X47" t="n">
-        <v>5.108179535392596</v>
+        <v>0.1227780247380687</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1227780247380687</v>
+        <v>8.046246763814068</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.046246763814068</v>
+        <v>1.709770449615942</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.709770449615942</v>
+        <v>10.38900916614558</v>
       </c>
       <c r="AB47" t="n">
-        <v>10.38900916006484</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.005546963710960306</v>
-      </c>
-      <c r="AD47" t="inlineStr">
+        <v>0.005546963694095464</v>
+      </c>
+      <c r="AC47" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD47" t="n">
+        <v>-0.580159604549408</v>
+      </c>
       <c r="AE47" t="n">
-        <v>4.108113765716553</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>6.427614212036133</v>
+        <v>9.937227249145508</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>726</v>
+      <c r="A48" t="n">
+        <v>42.0865253634753</v>
       </c>
       <c r="B48" t="n">
-        <v>42.0865253634753</v>
+        <v>11.61062958759157</v>
       </c>
       <c r="C48" t="n">
-        <v>11.61062958759157</v>
+        <v>30.20551982470235</v>
       </c>
       <c r="D48" t="n">
-        <v>30.20551982470235</v>
+        <v>7.933285538006333</v>
       </c>
       <c r="E48" t="n">
-        <v>7.933285538006333</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -5226,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>8.164039686224461</v>
       </c>
       <c r="O48" t="n">
-        <v>8.164039686224461</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -5241,65 +5103,62 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>0.05337959878309732</v>
       </c>
       <c r="T48" t="n">
-        <v>0.05337959878309732</v>
+        <v>1897.866015794312</v>
       </c>
       <c r="U48" t="n">
-        <v>1897.866015794312</v>
+        <v>263.3428581176036</v>
       </c>
       <c r="V48" t="n">
-        <v>263.3428581176036</v>
+        <v>-10.18430042650438</v>
       </c>
       <c r="W48" t="n">
-        <v>-10.18430042650438</v>
+        <v>5.978418731174595</v>
       </c>
       <c r="X48" t="n">
-        <v>5.978418731174595</v>
+        <v>0.1372934475010165</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1372934475010165</v>
+        <v>7.848168989507927</v>
       </c>
       <c r="Z48" t="n">
-        <v>7.848168989507927</v>
+        <v>1.849931607495227</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.849931607495227</v>
+        <v>10.7785422195612</v>
       </c>
       <c r="AB48" t="n">
-        <v>10.77854221136515</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.004565299744328621</v>
-      </c>
-      <c r="AD48" t="inlineStr">
+        <v>0.00456529972561992</v>
+      </c>
+      <c r="AC48" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD48" t="n">
+        <v>-0.3640829622745514</v>
+      </c>
       <c r="AE48" t="n">
-        <v>4.007191181182861</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>6.762137889862061</v>
+        <v>10.19110488891602</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>727</v>
+      <c r="A49" t="n">
+        <v>40.81585186348995</v>
       </c>
       <c r="B49" t="n">
-        <v>40.81585186348995</v>
+        <v>11.45538272157001</v>
       </c>
       <c r="C49" t="n">
-        <v>11.45538272157001</v>
+        <v>27.19589965294441</v>
       </c>
       <c r="D49" t="n">
-        <v>27.19589965294441</v>
+        <v>9.05861416233218</v>
       </c>
       <c r="E49" t="n">
-        <v>9.05861416233218</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5326,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>11.47425159966346</v>
       </c>
       <c r="O49" t="n">
-        <v>11.47425159966346</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -5341,65 +5200,62 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>0.06038257678424401</v>
       </c>
       <c r="T49" t="n">
-        <v>0.06038257678424401</v>
+        <v>1911.895943236241</v>
       </c>
       <c r="U49" t="n">
-        <v>1911.895943236241</v>
+        <v>273.266600994712</v>
       </c>
       <c r="V49" t="n">
-        <v>273.266600994712</v>
+        <v>-12.19586695638432</v>
       </c>
       <c r="W49" t="n">
-        <v>-12.19586695638432</v>
+        <v>6.628266439494642</v>
       </c>
       <c r="X49" t="n">
-        <v>6.628266439494642</v>
+        <v>0.1491778924153696</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1491778924153696</v>
+        <v>7.621670965023038</v>
       </c>
       <c r="Z49" t="n">
-        <v>7.621670965023038</v>
+        <v>1.957039338609674</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.957039338609674</v>
+        <v>12.9224503713978</v>
       </c>
       <c r="AB49" t="n">
-        <v>12.92245036453609</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0.001562879724392396</v>
-      </c>
-      <c r="AD49" t="inlineStr">
+        <v>0.001562879719030352</v>
+      </c>
+      <c r="AC49" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD49" t="n">
+        <v>-0.1898046880960464</v>
+      </c>
       <c r="AE49" t="n">
-        <v>4.004144668579102</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>6.957865238189697</v>
+        <v>10.3933801651001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>728</v>
+      <c r="A50" t="n">
+        <v>45.37200448015243</v>
       </c>
       <c r="B50" t="n">
-        <v>45.37200448015243</v>
+        <v>5.223833584071546</v>
       </c>
       <c r="C50" t="n">
-        <v>5.223833584071546</v>
+        <v>47.58367348944883</v>
       </c>
       <c r="D50" t="n">
-        <v>47.58367348944883</v>
+        <v>1.268955264287828</v>
       </c>
       <c r="E50" t="n">
-        <v>1.268955264287828</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -5426,10 +5282,10 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.5515331820393581</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5515331820393581</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -5441,65 +5297,62 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.01650675275345274</v>
       </c>
       <c r="T50" t="n">
-        <v>0.01650675275345274</v>
+        <v>1802.78064547813</v>
       </c>
       <c r="U50" t="n">
-        <v>1802.78064547813</v>
+        <v>141.3045690310867</v>
       </c>
       <c r="V50" t="n">
-        <v>141.3045690310867</v>
+        <v>-3.350434456507965</v>
       </c>
       <c r="W50" t="n">
-        <v>-3.350434456507965</v>
+        <v>2.142422444745051</v>
       </c>
       <c r="X50" t="n">
-        <v>2.142422444745051</v>
+        <v>0.07229919356232063</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.07229919356232063</v>
+        <v>8.770975246959415</v>
       </c>
       <c r="Z50" t="n">
-        <v>8.770975246959415</v>
+        <v>1.275115202946909</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.275115202946909</v>
+        <v>17.46343652512323</v>
       </c>
       <c r="AB50" t="n">
-        <v>17.46343652168439</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0.0001613849164684433</v>
-      </c>
-      <c r="AD50" t="inlineStr">
+        <v>0.0001613849161909986</v>
+      </c>
+      <c r="AC50" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD50" t="n">
+        <v>-1.139680743217468</v>
+      </c>
       <c r="AE50" t="n">
-        <v>3.77337908744812</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>5.038180351257324</v>
+        <v>8.399454116821289</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>729</v>
+      <c r="A51" t="n">
+        <v>48.78786662406539</v>
       </c>
       <c r="B51" t="n">
-        <v>48.78786662406539</v>
+        <v>6.144711966491161</v>
       </c>
       <c r="C51" t="n">
-        <v>6.144711966491161</v>
+        <v>42.64463011182583</v>
       </c>
       <c r="D51" t="n">
-        <v>42.64463011182583</v>
+        <v>1.746867803426478</v>
       </c>
       <c r="E51" t="n">
-        <v>1.746867803426478</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -5526,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.6759234941911552</v>
       </c>
       <c r="O51" t="n">
-        <v>0.6759234941911552</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -5541,65 +5394,62 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>0.01848949497671528</v>
       </c>
       <c r="T51" t="n">
-        <v>0.01848949497671528</v>
+        <v>1813.793750480788</v>
       </c>
       <c r="U51" t="n">
-        <v>1813.793750480788</v>
+        <v>156.2722053331537</v>
       </c>
       <c r="V51" t="n">
-        <v>156.2722053331537</v>
+        <v>-3.497233308448993</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.497233308448993</v>
+        <v>2.270210503507955</v>
       </c>
       <c r="X51" t="n">
-        <v>2.270210503507955</v>
+        <v>0.07679224333612204</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.07679224333612204</v>
+        <v>8.64196624642601</v>
       </c>
       <c r="Z51" t="n">
-        <v>8.64196624642601</v>
+        <v>1.299463027721608</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.299463027721608</v>
+        <v>15.7392783326859</v>
       </c>
       <c r="AB51" t="n">
-        <v>15.73927832678815</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.0003821722390566773</v>
-      </c>
-      <c r="AD51" t="inlineStr">
+        <v>0.0003821722379296899</v>
+      </c>
+      <c r="AC51" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD51" t="n">
+        <v>-1.338472127914429</v>
+      </c>
       <c r="AE51" t="n">
-        <v>4.030261516571045</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>5.115845680236816</v>
+        <v>8.676410675048828</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>730</v>
+      <c r="A52" t="n">
+        <v>50.73675625671652</v>
       </c>
       <c r="B52" t="n">
-        <v>50.73675625671652</v>
+        <v>6.684722573324661</v>
       </c>
       <c r="C52" t="n">
-        <v>6.684722573324661</v>
+        <v>39.73609779881278</v>
       </c>
       <c r="D52" t="n">
-        <v>39.73609779881278</v>
+        <v>1.918285343225266</v>
       </c>
       <c r="E52" t="n">
-        <v>1.918285343225266</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -5626,10 +5476,10 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.9241380279207699</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9241380279207699</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -5641,65 +5491,62 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>0.02093074681060939</v>
       </c>
       <c r="T52" t="n">
-        <v>0.02093074681060939</v>
+        <v>1819.810792892937</v>
       </c>
       <c r="U52" t="n">
-        <v>1819.810792892937</v>
+        <v>161.7862543444157</v>
       </c>
       <c r="V52" t="n">
-        <v>161.7862543444157</v>
+        <v>-3.723492075321114</v>
       </c>
       <c r="W52" t="n">
-        <v>-3.723492075321114</v>
+        <v>2.535657421572502</v>
       </c>
       <c r="X52" t="n">
-        <v>2.535657421572502</v>
+        <v>0.07998154867036784</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.07998154867036784</v>
+        <v>8.558739521406244</v>
       </c>
       <c r="Z52" t="n">
-        <v>8.558739521406244</v>
+        <v>1.321868675660055</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.321868675660055</v>
+        <v>15.42564541273058</v>
       </c>
       <c r="AB52" t="n">
-        <v>15.42564540521257</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.0004470577832872413</v>
-      </c>
-      <c r="AD52" t="inlineStr">
+        <v>0.0004470577816066967</v>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD52" t="n">
+        <v>-1.3471360206604</v>
+      </c>
       <c r="AE52" t="n">
-        <v>4.128252029418945</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>5.095830917358398</v>
+        <v>8.741044998168945</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>731</v>
+      <c r="A53" t="n">
+        <v>51.96609868449762</v>
       </c>
       <c r="B53" t="n">
-        <v>51.96609868449762</v>
+        <v>7.125557036648022</v>
       </c>
       <c r="C53" t="n">
-        <v>7.125557036648022</v>
+        <v>36.51395857641639</v>
       </c>
       <c r="D53" t="n">
-        <v>36.51395857641639</v>
+        <v>2.908620861069055</v>
       </c>
       <c r="E53" t="n">
-        <v>2.908620861069055</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -5726,10 +5573,10 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.485764841368929</v>
       </c>
       <c r="O53" t="n">
-        <v>1.485764841368929</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -5741,65 +5588,62 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>0.02613434287937934</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02613434287937934</v>
+        <v>1831.477901479313</v>
       </c>
       <c r="U53" t="n">
-        <v>1831.477901479313</v>
+        <v>182.6578015993563</v>
       </c>
       <c r="V53" t="n">
-        <v>182.6578015993563</v>
+        <v>-4.267143899904623</v>
       </c>
       <c r="W53" t="n">
-        <v>-4.267143899904623</v>
+        <v>3.037407874301898</v>
       </c>
       <c r="X53" t="n">
-        <v>3.037407874301898</v>
+        <v>0.087552317304962</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.087552317304962</v>
+        <v>8.448512326713377</v>
       </c>
       <c r="Z53" t="n">
-        <v>8.448512326713377</v>
+        <v>1.373272575262313</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.373272575262313</v>
+        <v>14.86411791037237</v>
       </c>
       <c r="AB53" t="n">
-        <v>14.86411790263286</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0.0005919674241804396</v>
-      </c>
-      <c r="AD53" t="inlineStr">
+        <v>0.0005919674218897164</v>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD53" t="n">
+        <v>-1.329067587852478</v>
+      </c>
       <c r="AE53" t="n">
-        <v>4.344599723815918</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>5.256979465484619</v>
+        <v>8.973010063171387</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>732</v>
+      <c r="A54" t="n">
+        <v>52.45736467440484</v>
       </c>
       <c r="B54" t="n">
-        <v>52.45736467440484</v>
+        <v>7.818356008967962</v>
       </c>
       <c r="C54" t="n">
-        <v>7.818356008967962</v>
+        <v>33.94381032547561</v>
       </c>
       <c r="D54" t="n">
-        <v>33.94381032547561</v>
+        <v>3.48038624477838</v>
       </c>
       <c r="E54" t="n">
-        <v>3.48038624477838</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -5826,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.300082746373203</v>
       </c>
       <c r="O54" t="n">
-        <v>2.300082746373203</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -5841,65 +5685,62 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>0.03136456619215159</v>
       </c>
       <c r="T54" t="n">
-        <v>0.03136456619215159</v>
+        <v>1841.294138540393</v>
       </c>
       <c r="U54" t="n">
-        <v>1841.294138540393</v>
+        <v>194.6042654912872</v>
       </c>
       <c r="V54" t="n">
-        <v>194.6042654912872</v>
+        <v>-5.013693058505862</v>
       </c>
       <c r="W54" t="n">
-        <v>-5.013693058505862</v>
+        <v>3.590387282908146</v>
       </c>
       <c r="X54" t="n">
-        <v>3.590387282908146</v>
+        <v>0.09506810679981141</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.09506810679981141</v>
+        <v>8.337360200103499</v>
       </c>
       <c r="Z54" t="n">
-        <v>8.337360200103499</v>
+        <v>1.439120569864712</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.439120569864712</v>
+        <v>14.62492050798479</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.62492049286846</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0.0006671736197574329</v>
-      </c>
-      <c r="AD54" t="inlineStr">
+        <v>0.000667173614714911</v>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD54" t="n">
+        <v>-1.343533635139465</v>
+      </c>
       <c r="AE54" t="n">
-        <v>4.397573471069336</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>5.589683055877686</v>
+        <v>9.319387435913086</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>733</v>
+      <c r="A55" t="n">
+        <v>51.85220057025387</v>
       </c>
       <c r="B55" t="n">
-        <v>51.85220057025387</v>
+        <v>8.53527245083175</v>
       </c>
       <c r="C55" t="n">
-        <v>8.53527245083175</v>
+        <v>31.97839661068264</v>
       </c>
       <c r="D55" t="n">
-        <v>31.97839661068264</v>
+        <v>4.252332960149705</v>
       </c>
       <c r="E55" t="n">
-        <v>4.252332960149705</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -5926,10 +5767,10 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.381797408082039</v>
       </c>
       <c r="O55" t="n">
-        <v>3.381797408082039</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -5941,65 +5782,62 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.03697844851397947</v>
       </c>
       <c r="T55" t="n">
-        <v>0.03697844851397947</v>
+        <v>1852.438872481081</v>
       </c>
       <c r="U55" t="n">
-        <v>1852.438872481081</v>
+        <v>208.8803546038069</v>
       </c>
       <c r="V55" t="n">
-        <v>208.8803546038069</v>
+        <v>-5.988293646345637</v>
       </c>
       <c r="W55" t="n">
-        <v>-5.988293646345637</v>
+        <v>4.163938861748861</v>
       </c>
       <c r="X55" t="n">
-        <v>4.163938861748861</v>
+        <v>0.1039704844714694</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.1039704844714694</v>
+        <v>8.222625121503787</v>
       </c>
       <c r="Z55" t="n">
-        <v>8.222625121503787</v>
+        <v>1.521481844261621</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.521481844261621</v>
+        <v>14.17624051707936</v>
       </c>
       <c r="AB55" t="n">
-        <v>14.17624049659472</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0.0008349654190374922</v>
-      </c>
-      <c r="AD55" t="inlineStr">
+        <v>0.0008349654104855553</v>
+      </c>
+      <c r="AC55" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD55" t="n">
+        <v>-1.14081072807312</v>
+      </c>
       <c r="AE55" t="n">
-        <v>4.366486072540283</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>5.878684520721436</v>
+        <v>9.601059913635254</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>734</v>
+      <c r="A56" t="n">
+        <v>51.37276147532685</v>
       </c>
       <c r="B56" t="n">
-        <v>51.37276147532685</v>
+        <v>8.790516358863357</v>
       </c>
       <c r="C56" t="n">
-        <v>8.790516358863357</v>
+        <v>29.88165140595067</v>
       </c>
       <c r="D56" t="n">
-        <v>29.88165140595067</v>
+        <v>4.817071318855069</v>
       </c>
       <c r="E56" t="n">
-        <v>4.817071318855069</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6026,10 +5864,10 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.137999441004045</v>
       </c>
       <c r="O56" t="n">
-        <v>5.137999441004045</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -6041,65 +5879,62 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.04386412301033653</v>
       </c>
       <c r="T56" t="n">
-        <v>0.04386412301033653</v>
+        <v>1861.438762891978</v>
       </c>
       <c r="U56" t="n">
-        <v>1861.438762891978</v>
+        <v>217.3992985995519</v>
       </c>
       <c r="V56" t="n">
-        <v>217.3992985995519</v>
+        <v>-7.404815575400058</v>
       </c>
       <c r="W56" t="n">
-        <v>-7.404815575400058</v>
+        <v>4.855416672966035</v>
       </c>
       <c r="X56" t="n">
-        <v>4.855416672966035</v>
+        <v>0.1135459249647726</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1135459249647726</v>
+        <v>8.085637514775369</v>
       </c>
       <c r="Z56" t="n">
-        <v>8.085637514775369</v>
+        <v>1.621859413550102</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.621859413550102</v>
+        <v>14.51495290014141</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.51495288861705</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0.0007048846085890847</v>
-      </c>
-      <c r="AD56" t="inlineStr">
+        <v>0.0007048846045274448</v>
+      </c>
+      <c r="AC56" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD56" t="n">
+        <v>-0.9443371295928955</v>
+      </c>
       <c r="AE56" t="n">
-        <v>4.454396724700928</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>6.22815990447998</v>
+        <v>9.983424186706543</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>735</v>
+      <c r="A57" t="n">
+        <v>49.881475732815</v>
       </c>
       <c r="B57" t="n">
-        <v>49.881475732815</v>
+        <v>9.097479396405918</v>
       </c>
       <c r="C57" t="n">
-        <v>9.097479396405918</v>
+        <v>27.44639767550942</v>
       </c>
       <c r="D57" t="n">
-        <v>27.44639767550942</v>
+        <v>6.385106315226083</v>
       </c>
       <c r="E57" t="n">
-        <v>6.385106315226083</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6126,10 +5961,10 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>7.189540880043592</v>
       </c>
       <c r="O57" t="n">
-        <v>7.189540880043592</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -6141,65 +5976,62 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.05056947647223296</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05056947647223296</v>
+        <v>1878.032354328183</v>
       </c>
       <c r="U57" t="n">
-        <v>1878.032354328183</v>
+        <v>238.9294845076311</v>
       </c>
       <c r="V57" t="n">
-        <v>238.9294845076311</v>
+        <v>-8.9391977369001</v>
       </c>
       <c r="W57" t="n">
-        <v>-8.9391977369001</v>
+        <v>5.441441972472609</v>
       </c>
       <c r="X57" t="n">
-        <v>5.441441972472609</v>
+        <v>0.1259856130237835</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.1259856130237835</v>
+        <v>7.91523055084948</v>
       </c>
       <c r="Z57" t="n">
-        <v>7.91523055084948</v>
+        <v>1.727016787533407</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.727016787533407</v>
+        <v>14.99902266451744</v>
       </c>
       <c r="AB57" t="n">
-        <v>14.99902265816707</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0.0005533547124426663</v>
-      </c>
-      <c r="AD57" t="inlineStr">
+        <v>0.0005533547106857384</v>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD57" t="n">
+        <v>-0.7348241806030273</v>
+      </c>
       <c r="AE57" t="n">
-        <v>4.371802806854248</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>6.471113204956055</v>
+        <v>10.01963329315186</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>736</v>
+      <c r="A58" t="n">
+        <v>46.147295090649</v>
       </c>
       <c r="B58" t="n">
-        <v>46.147295090649</v>
+        <v>8.858468480519768</v>
       </c>
       <c r="C58" t="n">
-        <v>8.858468480519768</v>
+        <v>25.79843573181753</v>
       </c>
       <c r="D58" t="n">
-        <v>25.79843573181753</v>
+        <v>7.658075855521748</v>
       </c>
       <c r="E58" t="n">
-        <v>7.658075855521748</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -6226,10 +6058,10 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>11.53772484149196</v>
       </c>
       <c r="O58" t="n">
-        <v>11.53772484149196</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -6241,65 +6073,62 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.06033155653299953</v>
       </c>
       <c r="T58" t="n">
-        <v>0.06033155653299953</v>
+        <v>1893.132140490695</v>
       </c>
       <c r="U58" t="n">
-        <v>1893.132140490695</v>
+        <v>252.9248188175117</v>
       </c>
       <c r="V58" t="n">
-        <v>252.9248188175117</v>
+        <v>-11.95489947297237</v>
       </c>
       <c r="W58" t="n">
-        <v>-11.95489947297237</v>
+        <v>6.429520058875785</v>
       </c>
       <c r="X58" t="n">
-        <v>6.429520058875785</v>
+        <v>0.1429482959700767</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.1429482959700767</v>
+        <v>7.666832004451789</v>
       </c>
       <c r="Z58" t="n">
-        <v>7.666832004451789</v>
+        <v>1.911541131955564</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.911541131955564</v>
+        <v>15.9700257548305</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.9700257427457</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0.0003405281131816373</v>
-      </c>
-      <c r="AD58" t="inlineStr">
+        <v>0.000340528111124061</v>
+      </c>
+      <c r="AC58" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD58" t="n">
+        <v>-0.4777270257472992</v>
+      </c>
       <c r="AE58" t="n">
-        <v>4.138594627380371</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>6.667025089263916</v>
+        <v>10.20939445495605</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>737</v>
+      <c r="A59" t="n">
+        <v>56.70921047332411</v>
       </c>
       <c r="B59" t="n">
-        <v>56.70921047332411</v>
+        <v>4.45933779448573</v>
       </c>
       <c r="C59" t="n">
-        <v>4.45933779448573</v>
+        <v>36.74922850445188</v>
       </c>
       <c r="D59" t="n">
-        <v>36.74922850445188</v>
+        <v>1.479037996335657</v>
       </c>
       <c r="E59" t="n">
-        <v>1.479037996335657</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -6326,10 +6155,10 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>0.6031852314026278</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6031852314026278</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -6341,65 +6170,62 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.01740178845315576</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01740178845315576</v>
+        <v>1809.884110433831</v>
       </c>
       <c r="U59" t="n">
-        <v>1809.884110433831</v>
+        <v>139.8836375896841</v>
       </c>
       <c r="V59" t="n">
-        <v>139.8836375896841</v>
+        <v>-3.031786591218217</v>
       </c>
       <c r="W59" t="n">
-        <v>-3.031786591218217</v>
+        <v>2.025358101991432</v>
       </c>
       <c r="X59" t="n">
-        <v>2.025358101991432</v>
+        <v>0.06936782305242623</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.06936782305242623</v>
+        <v>8.569387607330375</v>
       </c>
       <c r="Z59" t="n">
-        <v>8.569387607330375</v>
+        <v>1.203316242282515</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.203316242282515</v>
+        <v>21.94695370579473</v>
       </c>
       <c r="AB59" t="n">
-        <v>21.94695369331638</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.715060948226377e-05</v>
-      </c>
-      <c r="AD59" t="inlineStr">
+        <v>1.715060937523827e-05</v>
+      </c>
+      <c r="AC59" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD59" t="n">
+        <v>-1.546008229255676</v>
+      </c>
       <c r="AE59" t="n">
-        <v>4.273524284362793</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>5.072478771209717</v>
+        <v>8.751834869384766</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>738</v>
+      <c r="A60" t="n">
+        <v>58.23723423416003</v>
       </c>
       <c r="B60" t="n">
-        <v>58.23723423416003</v>
+        <v>4.536878620919904</v>
       </c>
       <c r="C60" t="n">
-        <v>4.536878620919904</v>
+        <v>34.31338024363218</v>
       </c>
       <c r="D60" t="n">
-        <v>34.31338024363218</v>
+        <v>1.953834188367503</v>
       </c>
       <c r="E60" t="n">
-        <v>1.953834188367503</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -6426,10 +6252,10 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>0.9586727129203946</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9586727129203946</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -6441,65 +6267,62 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.02130045397373641</v>
       </c>
       <c r="T60" t="n">
-        <v>0.02130045397373641</v>
+        <v>1815.769244665606</v>
       </c>
       <c r="U60" t="n">
-        <v>1815.769244665606</v>
+        <v>151.3022445361542</v>
       </c>
       <c r="V60" t="n">
-        <v>151.3022445361542</v>
+        <v>-3.339746289076316</v>
       </c>
       <c r="W60" t="n">
-        <v>-3.339746289076316</v>
+        <v>2.4274130012333</v>
       </c>
       <c r="X60" t="n">
-        <v>2.4274130012333</v>
+        <v>0.07376622362674641</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.07376622362674641</v>
+        <v>8.497920215669925</v>
       </c>
       <c r="Z60" t="n">
-        <v>8.497920215669925</v>
+        <v>1.229763406140413</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.229763406140413</v>
+        <v>22.08559921619565</v>
       </c>
       <c r="AB60" t="n">
-        <v>22.08559920076116</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1.600195588502551e-05</v>
-      </c>
-      <c r="AD60" t="inlineStr">
+        <v>1.600195576156871e-05</v>
+      </c>
+      <c r="AC60" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD60" t="n">
+        <v>-1.543697237968445</v>
+      </c>
       <c r="AE60" t="n">
-        <v>4.384980201721191</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>5.140256404876709</v>
+        <v>8.899381637573242</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>739</v>
+      <c r="A61" t="n">
+        <v>59.34611390594659</v>
       </c>
       <c r="B61" t="n">
-        <v>59.34611390594659</v>
+        <v>5.278994683623767</v>
       </c>
       <c r="C61" t="n">
-        <v>5.278994683623767</v>
+        <v>31.75357300774514</v>
       </c>
       <c r="D61" t="n">
-        <v>31.75357300774514</v>
+        <v>2.342432744028005</v>
       </c>
       <c r="E61" t="n">
-        <v>2.342432744028005</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -6526,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.278885658656497</v>
       </c>
       <c r="O61" t="n">
-        <v>1.278885658656497</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -6541,65 +6364,62 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>0.02418905334103039</v>
       </c>
       <c r="T61" t="n">
-        <v>0.02418905334103039</v>
+        <v>1823.822495380722</v>
       </c>
       <c r="U61" t="n">
-        <v>1823.822495380722</v>
+        <v>162.630477938699</v>
       </c>
       <c r="V61" t="n">
-        <v>162.630477938699</v>
+        <v>-3.626491216119732</v>
       </c>
       <c r="W61" t="n">
-        <v>-3.626491216119732</v>
+        <v>2.699405705324574</v>
       </c>
       <c r="X61" t="n">
-        <v>2.699405705324574</v>
+        <v>0.0788050276053151</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.0788050276053151</v>
+        <v>8.411801508251644</v>
       </c>
       <c r="Z61" t="n">
-        <v>8.411801508251644</v>
+        <v>1.262040669588086</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.262040669588086</v>
+        <v>22.54412228914518</v>
       </c>
       <c r="AB61" t="n">
-        <v>22.54412227327427</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1.272348401970547e-05</v>
-      </c>
-      <c r="AD61" t="inlineStr">
+        <v>1.272348391867517e-05</v>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD61" t="n">
+        <v>-1.605461239814758</v>
+      </c>
       <c r="AE61" t="n">
-        <v>4.467473030090332</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>5.261845588684082</v>
+        <v>8.911335945129395</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>740</v>
+      <c r="A62" t="n">
+        <v>59.33493295870724</v>
       </c>
       <c r="B62" t="n">
-        <v>59.33493295870724</v>
+        <v>5.752837488642101</v>
       </c>
       <c r="C62" t="n">
-        <v>5.752837488642101</v>
+        <v>29.99528848365004</v>
       </c>
       <c r="D62" t="n">
-        <v>29.99528848365004</v>
+        <v>2.914852635871863</v>
       </c>
       <c r="E62" t="n">
-        <v>2.914852635871863</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -6626,10 +6446,10 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.002088433128751</v>
       </c>
       <c r="O62" t="n">
-        <v>2.002088433128751</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -6641,65 +6461,62 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.02932879966732232</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02932879966732232</v>
+        <v>1831.956111086357</v>
       </c>
       <c r="U62" t="n">
-        <v>1831.956111086357</v>
+        <v>175.8022254655756</v>
       </c>
       <c r="V62" t="n">
-        <v>175.8022254655756</v>
+        <v>-4.296603370469128</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.296603370469128</v>
+        <v>3.233605779627207</v>
       </c>
       <c r="X62" t="n">
-        <v>3.233605779627207</v>
+        <v>0.08625357428706135</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.08625357428706135</v>
+        <v>8.326103638935868</v>
       </c>
       <c r="Z62" t="n">
-        <v>8.326103638935868</v>
+        <v>1.326537735811675</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.326537735811675</v>
+        <v>21.93479354435705</v>
       </c>
       <c r="AB62" t="n">
-        <v>21.93479353103735</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.72552042295715e-05</v>
-      </c>
-      <c r="AD62" t="inlineStr">
+        <v>1.725520411466341e-05</v>
+      </c>
+      <c r="AC62" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD62" t="n">
+        <v>-1.496286153793335</v>
+      </c>
       <c r="AE62" t="n">
-        <v>4.553428649902344</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>5.478067874908447</v>
+        <v>9.262004852294922</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>741</v>
+      <c r="A63" t="n">
+        <v>58.39353789451046</v>
       </c>
       <c r="B63" t="n">
-        <v>58.39353789451046</v>
+        <v>6.257907215926917</v>
       </c>
       <c r="C63" t="n">
-        <v>6.257907215926917</v>
+        <v>28.72947600949317</v>
       </c>
       <c r="D63" t="n">
-        <v>28.72947600949317</v>
+        <v>3.686192936964952</v>
       </c>
       <c r="E63" t="n">
-        <v>3.686192936964952</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -6726,10 +6543,10 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.932885943104509</v>
       </c>
       <c r="O63" t="n">
-        <v>2.932885943104509</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -6741,65 +6558,62 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>0.0346884499810637</v>
       </c>
       <c r="T63" t="n">
-        <v>0.0346884499810637</v>
+        <v>1841.442540380199</v>
       </c>
       <c r="U63" t="n">
-        <v>1841.442540380199</v>
+        <v>191.5431379373314</v>
       </c>
       <c r="V63" t="n">
-        <v>191.5431379373314</v>
+        <v>-5.15969551143198</v>
       </c>
       <c r="W63" t="n">
-        <v>-5.15969551143198</v>
+        <v>3.770269184798587</v>
       </c>
       <c r="X63" t="n">
-        <v>3.770269184798587</v>
+        <v>0.09500510175245287</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.09500510175245287</v>
+        <v>8.237211329330723</v>
       </c>
       <c r="Z63" t="n">
-        <v>8.237211329330723</v>
+        <v>1.407001033805207</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.407001033805207</v>
+        <v>20.87102970603369</v>
       </c>
       <c r="AB63" t="n">
-        <v>20.87102969221151</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>2.937064516750354e-05</v>
-      </c>
-      <c r="AD63" t="inlineStr">
+        <v>2.937064496455477e-05</v>
+      </c>
+      <c r="AC63" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD63" t="n">
+        <v>-1.287162184715271</v>
+      </c>
       <c r="AE63" t="n">
-        <v>4.662973880767822</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>5.784929275512695</v>
+        <v>9.578317642211914</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>742</v>
+      <c r="A64" t="n">
+        <v>57.3323684814925</v>
       </c>
       <c r="B64" t="n">
-        <v>57.3323684814925</v>
+        <v>6.626916797840604</v>
       </c>
       <c r="C64" t="n">
-        <v>6.626916797840604</v>
+        <v>27.03294124676937</v>
       </c>
       <c r="D64" t="n">
-        <v>27.03294124676937</v>
+        <v>4.283868902542922</v>
       </c>
       <c r="E64" t="n">
-        <v>4.283868902542922</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -6826,10 +6640,10 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.723904571354601</v>
       </c>
       <c r="O64" t="n">
-        <v>4.723904571354601</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -6841,65 +6655,62 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.0422622480706156</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0422622480706156</v>
+        <v>1850.859046094969</v>
       </c>
       <c r="U64" t="n">
-        <v>1850.859046094969</v>
+        <v>202.3200598468264</v>
       </c>
       <c r="V64" t="n">
-        <v>202.3200598468264</v>
+        <v>-6.655098692012342</v>
       </c>
       <c r="W64" t="n">
-        <v>-6.655098692012342</v>
+        <v>4.517802087094323</v>
       </c>
       <c r="X64" t="n">
-        <v>4.517802087094323</v>
+        <v>0.1061043392779721</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.1061043392779721</v>
+        <v>8.103649949123939</v>
       </c>
       <c r="Z64" t="n">
-        <v>8.103649949123939</v>
+        <v>1.525445472123222</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.525445472123222</v>
+        <v>20.46430820864764</v>
       </c>
       <c r="AB64" t="n">
-        <v>20.46430819420448</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>3.599415128174854e-05</v>
-      </c>
-      <c r="AD64" t="inlineStr">
+        <v>3.599415102184533e-05</v>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD64" t="n">
+        <v>-1.15434467792511</v>
+      </c>
       <c r="AE64" t="n">
-        <v>4.600523948669434</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>6.082609176635742</v>
+        <v>9.865531921386719</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>743</v>
+      <c r="A65" t="n">
+        <v>54.83283250514894</v>
       </c>
       <c r="B65" t="n">
-        <v>54.83283250514894</v>
+        <v>7.032440610391723</v>
       </c>
       <c r="C65" t="n">
-        <v>7.032440610391723</v>
+        <v>25.46424470379871</v>
       </c>
       <c r="D65" t="n">
-        <v>25.46424470379871</v>
+        <v>5.527364889749399</v>
       </c>
       <c r="E65" t="n">
-        <v>5.527364889749399</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -6926,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>7.143117290911234</v>
       </c>
       <c r="O65" t="n">
-        <v>7.143117290911234</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -6941,65 +6752,62 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>0.05021896804764987</v>
       </c>
       <c r="T65" t="n">
-        <v>0.05021896804764987</v>
+        <v>1865.499561822273</v>
       </c>
       <c r="U65" t="n">
-        <v>1865.499561822273</v>
+        <v>221.858194701114</v>
       </c>
       <c r="V65" t="n">
-        <v>221.858194701114</v>
+        <v>-8.564900557373438</v>
       </c>
       <c r="W65" t="n">
-        <v>-8.564900557373438</v>
+        <v>5.247073115973366</v>
       </c>
       <c r="X65" t="n">
-        <v>5.247073115973366</v>
+        <v>0.1202527212934408</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.1202527212934408</v>
+        <v>7.934625268674909</v>
       </c>
       <c r="Z65" t="n">
-        <v>7.934625268674909</v>
+        <v>1.667377773524082</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.667377773524082</v>
+        <v>19.69151636820112</v>
       </c>
       <c r="AB65" t="n">
-        <v>19.6915163463456</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>5.297141268822969e-05</v>
-      </c>
-      <c r="AD65" t="inlineStr">
+        <v>5.297141210935941e-05</v>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD65" t="n">
+        <v>-0.910956859588623</v>
+      </c>
       <c r="AE65" t="n">
-        <v>4.420213222503662</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>6.327803611755371</v>
+        <v>10.07173156738281</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>744</v>
+      <c r="A66" t="n">
+        <v>66.18771861830042</v>
       </c>
       <c r="B66" t="n">
-        <v>66.18771861830042</v>
+        <v>3.571193889207815</v>
       </c>
       <c r="C66" t="n">
-        <v>3.571193889207815</v>
+        <v>27.90815232372413</v>
       </c>
       <c r="D66" t="n">
-        <v>27.90815232372413</v>
+        <v>1.502033184039599</v>
       </c>
       <c r="E66" t="n">
-        <v>1.502033184039599</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -7026,10 +6834,10 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.8309019847280388</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8309019847280388</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -7041,65 +6849,62 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.01963192563019495</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01963192563019495</v>
+        <v>1813.904730364141</v>
       </c>
       <c r="U66" t="n">
-        <v>1813.904730364141</v>
+        <v>133.340212169379</v>
       </c>
       <c r="V66" t="n">
-        <v>133.340212169379</v>
+        <v>-2.8002327490981</v>
       </c>
       <c r="W66" t="n">
-        <v>-2.8002327490981</v>
+        <v>2.129102396816455</v>
       </c>
       <c r="X66" t="n">
-        <v>2.129102396816455</v>
+        <v>0.06650261904096777</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.06650261904096777</v>
+        <v>8.40449574691122</v>
       </c>
       <c r="Z66" t="n">
-        <v>8.40449574691122</v>
+        <v>1.124538934076214</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.124538934076214</v>
+        <v>34.12814370469872</v>
       </c>
       <c r="AB66" t="n">
-        <v>34.12814368803568</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>3.883003296678567e-08</v>
-      </c>
-      <c r="AD66" t="inlineStr">
+        <v>3.883003263371876e-08</v>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD66" t="n">
+        <v>-1.624679207801819</v>
+      </c>
       <c r="AE66" t="n">
-        <v>4.547086715698242</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>5.195213317871094</v>
+        <v>9.005003929138184</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>745</v>
+      <c r="A67" t="n">
+        <v>66.85471859160208</v>
       </c>
       <c r="B67" t="n">
-        <v>66.85471859160208</v>
+        <v>3.813661095882745</v>
       </c>
       <c r="C67" t="n">
-        <v>3.813661095882745</v>
+        <v>26.49154144135773</v>
       </c>
       <c r="D67" t="n">
-        <v>26.49154144135773</v>
+        <v>1.691522230009478</v>
       </c>
       <c r="E67" t="n">
-        <v>1.691522230009478</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -7126,10 +6931,10 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.148556641147982</v>
       </c>
       <c r="O67" t="n">
-        <v>1.148556641147982</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -7141,65 +6946,62 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>0.02251848971573794</v>
       </c>
       <c r="T67" t="n">
-        <v>0.02251848971573794</v>
+        <v>1817.718960748199</v>
       </c>
       <c r="U67" t="n">
-        <v>1817.718960748199</v>
+        <v>139.2109885145891</v>
       </c>
       <c r="V67" t="n">
-        <v>139.2109885145891</v>
+        <v>-3.060644452700787</v>
       </c>
       <c r="W67" t="n">
-        <v>-3.060644452700787</v>
+        <v>2.426542647739842</v>
       </c>
       <c r="X67" t="n">
-        <v>2.426542647739842</v>
+        <v>0.07007314791346538</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.07007314791346538</v>
+        <v>8.354293452070605</v>
       </c>
       <c r="Z67" t="n">
-        <v>8.354293452070605</v>
+        <v>1.149923918218327</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.149923918218327</v>
+        <v>34.44798852516583</v>
       </c>
       <c r="AB67" t="n">
-        <v>34.44798850815873</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>3.309133889128901e-08</v>
-      </c>
-      <c r="AD67" t="inlineStr">
+        <v>3.309133855822211e-08</v>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD67" t="n">
+        <v>-1.570632576942444</v>
+      </c>
       <c r="AE67" t="n">
-        <v>4.57982349395752</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>5.257256031036377</v>
+        <v>9.180055618286133</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>746</v>
+      <c r="A68" t="n">
+        <v>66.29608309198557</v>
       </c>
       <c r="B68" t="n">
-        <v>66.29608309198557</v>
+        <v>4.432612943819033</v>
       </c>
       <c r="C68" t="n">
-        <v>4.432612943819033</v>
+        <v>24.91437454526202</v>
       </c>
       <c r="D68" t="n">
-        <v>24.91437454526202</v>
+        <v>2.416458994822328</v>
       </c>
       <c r="E68" t="n">
-        <v>2.416458994822328</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -7226,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.940470424111047</v>
       </c>
       <c r="O68" t="n">
-        <v>1.940470424111047</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -7241,65 +7043,62 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>0.02857061409414813</v>
       </c>
       <c r="T68" t="n">
-        <v>0.02857061409414813</v>
+        <v>1827.3507335351</v>
       </c>
       <c r="U68" t="n">
-        <v>1827.3507335351</v>
+        <v>158.7023074897322</v>
       </c>
       <c r="V68" t="n">
-        <v>158.7023074897322</v>
+        <v>-3.792604049406814</v>
       </c>
       <c r="W68" t="n">
-        <v>-3.792604049406814</v>
+        <v>3.013182612607435</v>
       </c>
       <c r="X68" t="n">
-        <v>3.013182612607435</v>
+        <v>0.07966612253987757</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.07966612253987757</v>
+        <v>8.264353349839952</v>
       </c>
       <c r="Z68" t="n">
-        <v>8.264353349839952</v>
+        <v>1.229650020650664</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.229650020650664</v>
+        <v>32.59076559101513</v>
       </c>
       <c r="AB68" t="n">
-        <v>32.59076556872615</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>8.375392646087221e-08</v>
-      </c>
-      <c r="AD68" t="inlineStr">
+        <v>8.375392546167149e-08</v>
+      </c>
+      <c r="AC68" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD68" t="n">
+        <v>-1.508249044418335</v>
+      </c>
       <c r="AE68" t="n">
-        <v>4.677714347839355</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>5.5016188621521</v>
+        <v>9.334720611572266</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>747</v>
+      <c r="A69" t="n">
+        <v>65.32452373485688</v>
       </c>
       <c r="B69" t="n">
-        <v>65.32452373485688</v>
+        <v>4.818150837213522</v>
       </c>
       <c r="C69" t="n">
-        <v>4.818150837213522</v>
+        <v>24.40198458959529</v>
       </c>
       <c r="D69" t="n">
-        <v>24.40198458959529</v>
+        <v>2.83944115866238</v>
       </c>
       <c r="E69" t="n">
-        <v>2.83944115866238</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -7326,10 +7125,10 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.615899679671924</v>
       </c>
       <c r="O69" t="n">
-        <v>2.615899679671924</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -7341,65 +7140,62 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.0325884773783547</v>
       </c>
       <c r="T69" t="n">
-        <v>0.0325884773783547</v>
+        <v>1833.070883285166</v>
       </c>
       <c r="U69" t="n">
-        <v>1833.070883285166</v>
+        <v>169.0801681298954</v>
       </c>
       <c r="V69" t="n">
-        <v>169.0801681298954</v>
+        <v>-4.41709935748788</v>
       </c>
       <c r="W69" t="n">
-        <v>-4.41709935748788</v>
+        <v>3.409548023397951</v>
       </c>
       <c r="X69" t="n">
-        <v>3.409548023397951</v>
+        <v>0.08616037513956529</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.08616037513956529</v>
+        <v>8.209032957442462</v>
       </c>
       <c r="Z69" t="n">
-        <v>8.209032957442462</v>
+        <v>1.293647358636754</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.293647358636754</v>
+        <v>30.91008887932771</v>
       </c>
       <c r="AB69" t="n">
-        <v>30.91008884727232</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.94070484127451e-07</v>
-      </c>
-      <c r="AD69" t="inlineStr">
+        <v>1.940704810188265e-07</v>
+      </c>
+      <c r="AC69" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD69" t="n">
+        <v>-1.489788174629211</v>
+      </c>
       <c r="AE69" t="n">
-        <v>4.687490940093994</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>5.618652820587158</v>
+        <v>9.523708343505859</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>748</v>
+      <c r="A70" t="n">
+        <v>63.37031159981304</v>
       </c>
       <c r="B70" t="n">
-        <v>63.37031159981304</v>
+        <v>5.076981561592881</v>
       </c>
       <c r="C70" t="n">
-        <v>5.076981561592881</v>
+        <v>23.43996495381416</v>
       </c>
       <c r="D70" t="n">
-        <v>23.43996495381416</v>
+        <v>4.034033011020312</v>
       </c>
       <c r="E70" t="n">
-        <v>4.034033011020312</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -7426,10 +7222,10 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.078708873759598</v>
       </c>
       <c r="O70" t="n">
-        <v>4.078708873759598</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -7441,48 +7237,45 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>0.03980131080266931</v>
       </c>
       <c r="T70" t="n">
-        <v>0.03980131080266931</v>
+        <v>1844.869218212895</v>
       </c>
       <c r="U70" t="n">
-        <v>1844.869218212895</v>
+        <v>192.1751435798204</v>
       </c>
       <c r="V70" t="n">
-        <v>192.1751435798204</v>
+        <v>-5.701688642009428</v>
       </c>
       <c r="W70" t="n">
-        <v>-5.701688642009428</v>
+        <v>4.064608656287339</v>
       </c>
       <c r="X70" t="n">
-        <v>4.064608656287339</v>
+        <v>0.09862805660520312</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.09862805660520312</v>
+        <v>8.10149138925423</v>
       </c>
       <c r="Z70" t="n">
-        <v>8.10149138925423</v>
+        <v>1.41087388275249</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.41087388275249</v>
+        <v>28.7152726023569</v>
       </c>
       <c r="AB70" t="n">
-        <v>28.71527257242891</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>5.815108036211214e-07</v>
-      </c>
-      <c r="AD70" t="inlineStr">
+        <v>5.815107949613818e-07</v>
+      </c>
+      <c r="AC70" t="inlineStr">
         <is>
           <t>new NiCrMoTiFe data</t>
         </is>
       </c>
+      <c r="AD70" t="n">
+        <v>-1.361755609512329</v>
+      </c>
       <c r="AE70" t="n">
-        <v>4.64789867401123</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>5.893807411193848</v>
+        <v>9.674147605895996</v>
       </c>
     </row>
   </sheetData>
